--- a/extraction/kraton.xlsx
+++ b/extraction/kraton.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,10 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="MM/DD/YYYY"/>
-    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -72,7 +71,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -440,14 +439,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V63"/>
+  <dimension ref="A1:V75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
@@ -456,7 +455,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -590,7 +589,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>J.P. Morgan</t>
+          <t>J.P. Morgan (target)</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -615,7 +614,7 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Kraton's financial adviser (J.P. Morgan Securities LLC; only financial adviser named). First seen acting at Sept–Dec 2020 strategy meetings; engagement letter formally approved 08/11/2021 (p.36). Fee about $32 million, mostly contingent on closing (p.52).</t>
+          <t>Kraton's financial adviser; attended the Board's September, November and December 2020 strategy meetings and executed the corporate development plan. Board formally approved its engagement 08/11/2021; engagement letter dated 08/13/2021 (p. 6).</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -646,7 +645,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
+          <t>Kraton (target)</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -671,12 +670,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Board adopts corporate development plan: buy or combine with other polymer businesses and/or sell the CST business (part of chemical segment); not a whole-company sale. Talks with Party A and Party B on their polymer businesses (declined) are Kraton buying, no rows. Ref: $26.25 close 12/14/2020.</t>
+          <t>Board authorizes a corporate development plan: acquire or combine with other parties' polymer businesses and/or sell the crude sulfate turpentine (CST) business, part of the chemical segment. Not a whole-company sale. Ref: $26.25 close 12/14/2020.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>“The Board authorized Kraton’s senior management and J.P. Morgan to pursue this corporate development plan and discuss potential transactions in furtherance of the plan with third parties.” (p. 32)</t>
+          <t>“On December 14, 2020, the date on which the Board authorized Kraton to pursue the corporate development plan” (p. 32)</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -706,7 +705,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Party C; Party D; Party E; Party G</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -731,13 +730,13 @@
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated talks (management and J.P. Morgan) under #2 on selling the CST business only; each said it might be interested, subject to diligence. Window runs from #2 to the 05/20/2021 update. Not entry.</t>
+          <t>Target-initiated: Kraton management and J.P. Morgan discussed a sale of the CST business (segment only) under the corporate development plan. Party C said it might be interested, subject to further diligence and analysis. Window: after 12/14/2020 authorization, before 05/20/2021 Board review.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -745,14 +744,10 @@
           <t>“Each of Party C, Party D, Party E, and Party G informed Kraton that they might be interested in acquiring Kraton’s CST business, subject to further diligence and analysis.” (p. 32)</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q2</t>
-        </is>
-      </c>
+      <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
       <c r="T4" s="3" t="n">
-        <v>44179</v>
+        <v>44257</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>44179</v>
@@ -772,7 +767,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Party F</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -803,22 +798,18 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated CST talks under #2; Party F declined. Never entered.</t>
+          <t>Target-initiated: Kraton management and J.P. Morgan discussed a sale of the CST business (segment only) under the corporate development plan. Party D said it might be interested, subject to further diligence and analysis. Window: after 12/14/2020 authorization, before 05/20/2021 Board review.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>“Party F informed Kraton that it was not interested in acquiring Kraton’s CST business.” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“Each of Party C, Party D, Party E, and Party G informed Kraton that they might be interested in acquiring Kraton’s CST business, subject to further diligence and analysis.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
       <c r="T5" s="3" t="n">
-        <v>44179</v>
+        <v>44257</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>44179</v>
@@ -833,18 +824,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/20/2021</t>
+          <t>late 2020 – early 2021</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>King &amp; Spalding LLP</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
+          <t>Party E</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -858,26 +853,28 @@
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
+      <c r="M6" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Kraton's legal adviser; first seen acting at the 05/20/2021 board meeting. Advised on fiduciary duties, drafted the merger agreement and negotiated it with Parent's counsel O'Melveny (#52).</t>
+          <t>Target-initiated: Kraton management and J.P. Morgan discussed a sale of the CST business (segment only) under the corporate development plan. Party E said it might be interested, subject to further diligence and analysis. Window: after 12/14/2020 authorization, before 05/20/2021 Board review.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>“Representatives of J.P. Morgan and King &amp; Spalding LLP, Kraton’s legal advisor, also participated in the meeting.” (p. 32)</t>
+          <t>“Each of Party C, Party D, Party E, and Party G informed Kraton that they might be interested in acquiring Kraton’s CST business, subject to further diligence and analysis.” (p. 32)</t>
         </is>
       </c>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="3" t="n">
-        <v>44336</v>
+        <v>44257</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>44336</v>
+        <v>44179</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>44336</v>
@@ -889,18 +886,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/20/2021</t>
+          <t>late 2020 – early 2021</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
+          <t>Party G</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -914,30 +915,28 @@
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Board decides to explore a sale of all of Kraton after the plan gained no momentum; orders a buyer list, timeline and process for review the next week. CST proposals from C, D, E, G to be weighed against whole-company bids. Ref: $33.82 close 05/20/2021.</t>
+          <t>Target-initiated: Kraton management and J.P. Morgan discussed a sale of the CST business (segment only) under the corporate development plan. Party G said it might be interested, subject to further diligence and analysis. Window: after 12/14/2020 authorization, before 05/20/2021 Board review.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>“the Board determined that it would be in the best interests of Kraton and its stockholders to explore the potential sale of all of Kraton” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“Each of Party C, Party D, Party E, and Party G informed Kraton that they might be interested in acquiring Kraton’s CST business, subject to further diligence and analysis.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
       <c r="T7" s="3" t="n">
-        <v>44336</v>
+        <v>44257</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>44336</v>
+        <v>44179</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>44336</v>
@@ -949,58 +948,60 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>05/24/2021</t>
+          <t>late 2020 – early 2021</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n"/>
+          <t>Party F</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
+      <c r="M8" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Board reviews list of 14 potential buyers (strategic, financial, sponsors with chemical/polymer holdings) and directs outreach and a two-phase process: first-round IOIs on public information, highest-value bidders to a second round. Outreach (#8) is its direct execution from end of May. Ref: $34.33 close.</t>
+          <t>Target-initiated discussion of a sale of the CST business (segment only). Party F declined: not interested. Never entered. Window: after 12/14/2020 authorization, before 05/20/2021 Board review.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“the Board directed Kraton’s senior management to work with J.P. Morgan to contact the 14 possible acquirers that were discussed at the meeting” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“Party F informed Kraton that it was not interested in acquiring Kraton’s CST business.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="3" t="n">
-        <v>44340</v>
+        <v>44257</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>44340</v>
+        <v>44179</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>44340</v>
+        <v>44336</v>
       </c>
     </row>
     <row r="9">
@@ -1009,60 +1010,54 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>end of May – June 2021</t>
+          <t>05/20/2021</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14 listed parties (incl. Party A, Party B’s parent, Parent)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+          <t>King &amp; Spalding LLP (target)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n">
-        <v>14</v>
-      </c>
+      <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Target-led outreach by management and J.P. Morgan. Of the 14, nine signed NDAs (#11, #12) and five declined (p.34). Parties told a whole-company deal was preferred but stock deals or segment sales would be considered. Party B's parent is not followed further.</t>
+          <t>Kraton's legal adviser; first shown acting at the 05/20/2021 Board meeting; advised on fiduciary duties and the merger agreement through signing.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“contacted each of the 14 parties discussed with the Board at its May 24, 2021 meeting to explore the parties’ respective interest in a potential acquisition of Kraton” (p. 34)</t>
+          <t>“Representatives of J.P. Morgan and King &amp; Spalding LLP, Kraton’s legal advisor, also participated in the meeting.” (p. 32)</t>
         </is>
       </c>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>44340</v>
+        <v>44336</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>44340</v>
+        <v>44336</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>44377</v>
+        <v>44336</v>
       </c>
     </row>
     <row r="10">
@@ -1071,64 +1066,58 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>end of May – June 2021</t>
+          <t>05/20/2021</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Unnamed inbound strategic party</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kraton (target)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Inbound approach to J.P. Morgan from a strategic party not on the list; outside the 14. It signed an NDA (inside #11). The filing does not say whether it is one of the later-named parties.</t>
+          <t>Corporate development plan had gained no momentum; Board decides to explore a sale of all of Kraton, orders a buyer list and timeline for review the next week, and will weigh any CST proposals (Parties C, D, E, G) against whole-company proposals. Ref: $33.82 close 05/20/2021.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>“a potential strategic acquirer that was not included on the list of possible acquirers made an “inbound” inquiry and contacted representatives of J.P. Morgan regarding a potential acquisition of Kraton” (p. 34)</t>
+          <t>“the Board determined that it would be in the best interests of Kraton and its stockholders to explore the potential sale of all of Kraton” (p. 33)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="3" t="n">
-        <v>44356</v>
+        <v>44336</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>44336</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>44377</v>
+        <v>44336</v>
       </c>
     </row>
     <row r="11">
@@ -1137,22 +1126,18 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>June 2021</t>
+          <t>05/24/2021</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Party C; Party D; Party E; Party G</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kraton (target)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1166,35 +1151,33 @@
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Admits to CST diligence: management holds preliminary meetings on the CST business with C, D, E and G, separate from the whole-company meetings. Treated as their entry (other-scope). Date to set by Party E's exit (#17).</t>
+          <t>Board reviews list of strategic, financial and sponsor-with-portfolio-company buyers (incl. Party A, Party B's parent, Parent); plans two-phase process: IOIs on public information in third week of June, highest-value bidders to a second round. Outreach began end of May. Ref: $34.33 close 05/24/2021.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“Kraton’s senior management also participated in preliminary management meetings with Party C, Party D, Party E, and Party G regarding the potential sale of Kraton’s CST business.” (p. 34)</t>
+          <t>“the Board directed Kraton’s senior management to work with J.P. Morgan to contact the 14 possible acquirers that were discussed at the meeting to explore their interest” (p. 33)</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="3" t="n">
-        <v>44356</v>
+        <v>44340</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>44348</v>
+        <v>44340</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>44365</v>
+        <v>44340</v>
       </c>
     </row>
     <row r="12">
@@ -1203,22 +1186,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>by late June 2021</t>
+          <t>end of May and June 2021</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6 strategic NDA signers (incl. inbound party)</t>
+          <t>14 listed possible acquirers</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -1233,23 +1216,23 @@
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Filing total: 10 NDA parties (6 strategic, 4 financial), with standstills lapsing on announcement of a sale. Includes the inbound party (#9); assumed to include Party A, Parent, Party J and Party K. Five attended June management meetings.</t>
+          <t>Target-initiated outreach by management/J.P. Morgan; includes Party A, Party B's parent and Parent. Told whole-company bids preferred but stock deals or segment sales would be considered. Five contacted parties declined NDAs; exact arithmetic: 14 − 5 = 9 signed.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>“confidentiality agreements with 10 parties (including the party that made the “inbound” inquiry), six of which parties were potential strategic acquirers and four of which were potential financial acquirers” (p. 34)</t>
+          <t>“contacted each of the 14 parties discussed with the Board at its May 24, 2021 meeting to explore the parties’ respective interest in a potential acquisition of Kraton” (p. 34)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S12" s="2" t="n"/>
@@ -1269,22 +1252,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>by late June 2021</t>
+          <t>end of May and June 2021</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4 financial NDA signers</t>
+          <t>Unnamed strategic inbound party</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -1299,25 +1282,21 @@
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Remainder of the 10-party total in #11. Assumed to include Party H and Party I. All four attended preliminary management meetings in June (near-term performance, innovation projects).</t>
+          <t>Inbound inquiry to J.P. Morgan by a strategic party not on the Board's list; it later signed an NDA (counted in the six strategic signers, next row).</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>“confidentiality agreements with 10 parties (including the party that made the “inbound” inquiry), six of which parties were potential strategic acquirers and four of which were potential financial acquirers” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“a potential strategic acquirer that was not included on the list of possible acquirers made an “inbound” inquiry and contacted representatives of J.P. Morgan regarding a potential acquisition of Kraton” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="3" t="n">
         <v>44358</v>
@@ -1335,12 +1314,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>by 07/02/2021</t>
+          <t>by late June 2021</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>6 strategic NDA signers</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1350,7 +1329,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1361,39 +1340,27 @@
       </c>
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Portion of the CST business for $100 million total; no per-share price. Conditions not reported. Not solicited by the process letter; board held it for evaluation alongside whole-company bids.</t>
+          <t>Stated total 10 NDAs: 6 strategic (incl. inbound party), 4 financial; standstills lapse on an announced definitive agreement. June preliminary management meetings (near-term performance, innovation projects) for 9 signers (5 strategic, 4 financial). Party A, Parent, Party J, Party K presumed members, not stated.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>“Party C proposed acquiring a portion of Kraton’s CST business for $100 million” (p. 35)</t>
+          <t>“By late June 2021, Kraton had entered into confidentiality agreements with 10 parties (including the party that made the “inbound” inquiry), six of which parties were potential strategic acquirers” (p. 34)</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Q2; Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
@@ -1401,10 +1368,10 @@
         <v>44358</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>44337</v>
+        <v>44340</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>44379</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="15">
@@ -1413,22 +1380,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>by 07/02/2021</t>
+          <t>by late June 2021</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Party G</t>
+          <t>4 financial NDA signers</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1439,39 +1406,27 @@
       </c>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Portion of the CST business for $330 million total, subject to adjustments (unspecified); no per-share price. Held for evaluation with whole-company bids.</t>
+          <t>Part of the stated 10 NDAs (6 strategic, 4 financial), standstills included; all four attended June preliminary management meetings. Party H and Party I presumed members, not stated.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>“Party G proposed acquiring a portion of Kraton’s CST business for $330 million, subject to adjustments” (p. 35)</t>
+          <t>“six of which parties were potential strategic acquirers and four of which were potential financial acquirers” (p. 34)</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Q2; Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S15" s="2" t="n"/>
@@ -1479,10 +1434,10 @@
         <v>44358</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>44337</v>
+        <v>44340</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>44379</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="16">
@@ -1496,13 +1451,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n"/>
+          <t>Parties C, D, E and G</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1516,33 +1475,35 @@
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
+      <c r="M16" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>J.P. Morgan's process letter to every NDA signer asks for initial IOIs by 06/29/2021 and bars talks with management about post-closing roles. The board had planned IOIs for the third week of June.</t>
+          <t>Kraton admits the four CST-interested parties to preliminary management meetings on a CST-only sale; treated as their entry (segment scope, not whole company). Window ends 06/17/2021 because Party E withdrew 06/18/2021.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“circulated a process letter to each party that executed a confidentiality agreement that requested initial indications of interest be submitted by June 29, 2021” (p. 34)</t>
+          <t>“Kraton’s senior management also participated in preliminary management meetings with Party C, Party D, Party E, and Party G regarding the potential sale of Kraton’s CST business.” (p. 34)</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="3" t="n">
-        <v>44361</v>
+        <v>44358</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>44375</v>
+        <v>44364</v>
       </c>
     </row>
     <row r="17">
@@ -1556,17 +1517,13 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Unnamed strategic NDA signer</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kraton (target)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1580,35 +1537,29 @@
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Declined its preliminary management meeting and told J.P. Morgan it was no longer interested. Strategic by arithmetic: 6 strategic signers − 5 strategic meeting attendees = 1.</t>
+          <t>J.P. Morgan's process letter to every NDA signer asks for initial indications of interest by 06/29/2021; bars discussion of management's post-closing roles. Sent before the due date.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“One party that executed a confidentiality agreement with Kraton was invited to, but declined to participate in, this preliminary management meeting” (p. 34)</t>
+          <t>“circulated a process letter to each party that executed a confidentiality agreement that requested initial indications of interest be submitted by June 29, 2021” (p. 34)</t>
         </is>
       </c>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="n">
-        <v>44362</v>
+        <v>44361</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>44377</v>
+        <v>44375</v>
       </c>
     </row>
     <row r="18">
@@ -1617,12 +1568,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/18/2021</t>
+          <t>June 2021</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Unnamed strategic NDA signer</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1657,28 +1608,24 @@
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>CST-only participant (#10); no longer interested in the CST business. Bidder decided.</t>
+          <t>Declined the preliminary management meeting and said it was no longer interested. Type by exact arithmetic: 6 strategic signers − 5 strategic attendees = 1; all 4 financial attended.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“On June 18, 2021, Party E informed Kraton that it was no longer interested in acquiring Kraton’s CST business.” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>“declined to participate in, this preliminary management meeting and informed representatives of J.P. Morgan that it was no longer interested in pursuing a potential transaction” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="3" t="n">
-        <v>44365</v>
+        <v>44362</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>44365</v>
+        <v>44348</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>44365</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="19">
@@ -1687,12 +1634,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/23/2021</t>
+          <t>06/18/2021</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1727,28 +1674,28 @@
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>CST-only participant (#10); no longer interested in the CST business. Bidder decided.</t>
+          <t>CST-only participant: no longer interested in acquiring the CST business. Never bid.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“On June 23, 2021, Party D informed Kraton that it was no longer interested in acquiring Kraton’s CST business.” (p. 34)</t>
+          <t>“On June 18, 2021, Party E informed Kraton that it was no longer interested in acquiring Kraton’s CST business.” (p. 34)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>44370</v>
+        <v>44365</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>44370</v>
+        <v>44365</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>44370</v>
+        <v>44365</v>
       </c>
     </row>
     <row r="20">
@@ -1757,12 +1704,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>by 07/02/2021</t>
+          <t>06/23/2021</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1772,7 +1719,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -1781,52 +1728,44 @@
       <c r="G20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: preliminary diligence and management meetings in June; fuller diligence materials only after 07/20. First-round IOI (non-binding). Ref: $31.65 close 07/02/2021.</t>
+          <t>CST-only participant: no longer interested in acquiring the CST business. Never bid.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $42.00 to $45.00, Party H, a financial acquirer, proposed $41.00 to $43.00, Parent proposed $41.00, and Party I, a financial acquirer, proposed $40.00” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="n"/>
+          <t>“On June 23, 2021, Party D informed Kraton that it was no longer interested in acquiring Kraton’s CST business.” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>44376</v>
+        <v>44370</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>44348</v>
+        <v>44370</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>44379</v>
+        <v>44370</v>
       </c>
     </row>
     <row r="21">
@@ -1835,22 +1774,18 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>by 07/02/2021</t>
+          <t>06/29/2021</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Party H</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Kraton (target)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -1859,52 +1794,38 @@
       <c r="G21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: preliminary diligence and management meetings in June; fuller diligence materials only after 07/20. First-round IOI.</t>
+          <t>Due date for first-round indications of interest. Four whole-company IOIs received by 07/02/2021; exact arrival days not stated.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $42.00 to $45.00, Party H, a financial acquirer, proposed $41.00 to $43.00, Parent proposed $41.00, and Party I, a financial acquirer, proposed $40.00” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="n"/>
+          <t>“requested initial indications of interest be submitted by June 29, 2021” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="3" t="n">
         <v>44376</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>44348</v>
+        <v>44376</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>44379</v>
+        <v>44376</v>
       </c>
     </row>
     <row r="22">
@@ -1918,7 +1839,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1938,10 +1859,10 @@
         <v>1</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -1965,12 +1886,12 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: preliminary diligence and management meetings in June; fuller diligence materials only after 07/20. First-round IOI. Parent is a Korean petrochemical company (DL Holdings subsidiary) that bought Kraton's Cariflex business in 2020 (p.29).</t>
+          <t>No conditions stated; IOI based primarily on public information, diligence still open. Non-binding first-round indication of interest, $42.00–$45.00 per share. Ref: $31.65 close 07/02/2021.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $42.00 to $45.00, Party H, a financial acquirer, proposed $41.00 to $43.00, Parent proposed $41.00, and Party I, a financial acquirer, proposed $40.00” (p. 35)</t>
+          <t>“Party A proposed $42.00 to $45.00, Party H, a financial acquirer, proposed $41.00 to $43.00, Parent proposed $41.00, and Party I, a financial acquirer, proposed $40.00.” (p. 35)</t>
         </is>
       </c>
       <c r="R22" s="2" t="n"/>
@@ -1996,7 +1917,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Party I</t>
+          <t>Party H</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2016,10 +1937,10 @@
         <v>1</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2043,12 +1964,12 @@
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: preliminary diligence and management meetings in June; fuller diligence materials only after 07/20. First-round IOI.</t>
+          <t>No conditions stated; IOI based primarily on public information, diligence still open. First-round indication of interest, $41.00–$43.00 per share.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $42.00 to $45.00, Party H, a financial acquirer, proposed $41.00 to $43.00, Parent proposed $41.00, and Party I, a financial acquirer, proposed $40.00” (p. 35)</t>
+          <t>“Party A proposed $42.00 to $45.00, Party H, a financial acquirer, proposed $41.00 to $43.00, Parent proposed $41.00, and Party I, a financial acquirer, proposed $40.00.” (p. 35)</t>
         </is>
       </c>
       <c r="R23" s="2" t="n"/>
@@ -2074,7 +1995,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Party K</t>
+          <t>Parent (DL Chemical)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2084,7 +2005,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -2093,8 +2014,12 @@
       <c r="G24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
+      <c r="H24" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>41</v>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -2107,7 +2032,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -2117,19 +2042,15 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Significant diligence and firm financing commitments outstanding (reported 08/30, p.37). Chemical segment only, at 9.0x–10.0x trailing-12-month adjusted EBITDA to June 2021; no per-share price. Would not do a back-to-back sale with a polymer buyer.</t>
+          <t>No conditions stated; IOI based primarily on public information, diligence still open. First-round indication of interest at $41.00 per share. Parent (Korean petrochemical company, DL Holdings subsidiary) bought Kraton's Cariflex business in 2020 (p. 29).</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“Party K, a potential strategic acquirer, proposed acquiring Kraton’s chemical segment.” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>“Party A proposed $42.00 to $45.00, Party H, a financial acquirer, proposed $41.00 to $43.00, Parent proposed $41.00, and Party I, a financial acquirer, proposed $40.00.” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
       <c r="T24" s="3" t="n">
         <v>44376</v>
@@ -2147,18 +2068,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>06/29/2021</t>
+          <t>by 07/02/2021</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n"/>
+          <t>Party I</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -2167,38 +2092,52 @@
       <c r="G25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="n"/>
-      <c r="M25" s="2" t="n"/>
+      <c r="H25" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>First-round due date. By 07/02: four whole-company IOIs (#19–#22) and Party K's segment bid (#23); arrival days not stated. Party J said it would bid in mid-July; its 07/19 IOI (#28) was accepted late.</t>
+          <t>No conditions stated; IOI based primarily on public information, diligence still open. First-round indication of interest at $40.00 per share.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“By July 2, 2021, Kraton received four indications of interest as part of the first-round process that contemplated a potential acquisition of all of Kraton.” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
+          <t>“Party A proposed $42.00 to $45.00, Party H, a financial acquirer, proposed $41.00 to $43.00, Parent proposed $41.00, and Party I, a financial acquirer, proposed $40.00.” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="3" t="n">
         <v>44376</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>44376</v>
+        <v>44348</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>44376</v>
+        <v>44379</v>
       </c>
     </row>
     <row r="26">
@@ -2207,17 +2146,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>by 06/29/2021</t>
+          <t>by 07/02/2021</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>3 unnamed NDA signers (1 strategic, 2 financial)</t>
+          <t>Party J</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2237,31 +2176,27 @@
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Other stated reason</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Arithmetic: 10 signers − 1 withdrew (#16) − 5 first-round bidders (A, H, Parent, I, K) − Party J (bid late) = 3, if J and K are NDA signers. Never mentioned again. Split: 6−1−4 strategic = 1; 4−2 financial = 2.</t>
+          <t>No IOI by the 06/29/2021 due date; J told J.P. Morgan it intended to bid in mid-July. Treated as a presumed NDA signer eligible for round 1. Re-enters at #43.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“Kraton received four indications of interest as part of the first-round process” (p. 35)</t>
+          <t>“Party J, a strategic acquirer, informed representatives of J.P. Morgan that it intended to submit a proposal to acquire Kraton during the middle of July.” (p. 35)</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q5</t>
+          <t>Q2; Q5</t>
         </is>
       </c>
       <c r="S26" s="2" t="n"/>
@@ -2279,58 +2214,74 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>07/06/2021</t>
+          <t>by 07/02/2021</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n"/>
+          <t>Party K</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="n"/>
-      <c r="M27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Board asks Party A, Party H, Parent and Party I for updated IOIs of greater value by 07/19 (filing prints 'July 19, 2020') before choosing second-round bidders. C, G and K not asked to revise; J's promised bid awaited.</t>
+          <t>Heavy: J.P. Morgan later reported this proposal subject to significant diligence and firm financing commitments (p. 37); only a standalone deal, no back-to-back polymer sale. Chemical segment at 9.0x–10.0x trailing-12-month (June 2021) segment adjusted EBITDA; no price stated.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“the Board would require updated indications of interest to be received by July 19, 2020 that ascribed a greater value to Kraton” (p. 35)</t>
+          <t>“Party K, a potential strategic acquirer, proposed acquiring Kraton’s chemical segment.” (p. 35)</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q5</t>
+          <t>Q2; Q3</t>
         </is>
       </c>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="3" t="n">
-        <v>44383</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>44383</v>
-      </c>
+        <v>44376</v>
+      </c>
+      <c r="U27" s="2" t="n"/>
       <c r="V27" s="3" t="n">
-        <v>44383</v>
+        <v>44379</v>
       </c>
     </row>
     <row r="28">
@@ -2339,25 +2290,29 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/06/2021</t>
+          <t>by 06/29/2021</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n"/>
+          <t>Remaining strategic NDA signers (unnamed)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
@@ -2365,28 +2320,38 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Media rumour: Reuters reports Kraton hired J.P. Morgan for a possible sale. Six inbound inquiries followed (#39, #40). Ref: $36.37 close 07/06/2021; $34.51–$42.80 from then to signing.</t>
+          <t>Count: 1–5. Six strategic signers − 1 withdrawal (#17) = 5, less Party A, Parent, Party J (own row) and Party K if they were signers (likely, not stated): exactly 1 if all four were. No submission reported.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“Reuters published a report stating, among other matters, that Kraton had hired J.P. Morgan as its financial advisor to advise Kraton with respect to a potential sale of the company.” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="n"/>
+          <t>“By July 2, 2021, Kraton received four indications of interest as part of the first-round process that contemplated a potential acquisition of all of Kraton.” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="3" t="n">
-        <v>44383</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>44383</v>
-      </c>
+        <v>44376</v>
+      </c>
+      <c r="U28" s="2" t="n"/>
       <c r="V28" s="3" t="n">
-        <v>44383</v>
+        <v>44376</v>
       </c>
     </row>
     <row r="29">
@@ -2395,22 +2360,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>by 07/19/2021</t>
+          <t>by 06/29/2021</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Party J</t>
+          <t>Remaining financial NDA signers (unnamed)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2419,56 +2384,44 @@
       <c r="G29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: preliminary diligence and management meetings in June; fuller diligence materials only after 07/20. Late answer to the first-round letter (J said by 07/02 it would bid mid-July; still pending 07/06). Not asked in round 2. J said it would not exceed this range.</t>
+          <t>Count: 2–4. Four financial signers less Party H and Party I if they were signers (likely, not stated): exactly 2 if both were. No submission reported.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“Party J also submitted an indication of interest that proposed an acquisition of Kraton at a per share purchase price of $38.00 to $41.00 per share.” (p. 36)</t>
+          <t>“By July 2, 2021, Kraton received four indications of interest as part of the first-round process that contemplated a potential acquisition of all of Kraton.” (p. 35)</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S29" s="2" t="n"/>
       <c r="T29" s="3" t="n">
-        <v>44389</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>44383</v>
-      </c>
+        <v>44376</v>
+      </c>
+      <c r="U29" s="2" t="n"/>
       <c r="V29" s="3" t="n">
-        <v>44396</v>
+        <v>44376</v>
       </c>
     </row>
     <row r="30">
@@ -2477,12 +2430,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>by 07/19/2021</t>
+          <t>by 07/02/2021</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2492,21 +2445,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -2529,24 +2478,26 @@
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: preliminary diligence and management meetings in June; fuller diligence materials only after 07/20. Updated IOI, up from $42.00–$45.00 (#19).</t>
+          <t>Unclear: no condition stated; earlier interest was subject to further diligence. Proposes to buy a portion of the CST business for $100 million (total, not per share).</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $45.00, Party H proposed $42.00 to $45.00, and Parent proposed $45.00” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="n"/>
+          <t>“Party C proposed acquiring a portion of Kraton’s CST business for $100 million” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="3" t="n">
-        <v>44396</v>
-      </c>
-      <c r="U30" s="3" t="n">
-        <v>44383</v>
-      </c>
+        <v>44379</v>
+      </c>
+      <c r="U30" s="2" t="n"/>
       <c r="V30" s="3" t="n">
-        <v>44396</v>
+        <v>44379</v>
       </c>
     </row>
     <row r="31">
@@ -2555,36 +2506,32 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>by 07/19/2021</t>
+          <t>by 07/02/2021</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Party H</t>
+          <t>Party G</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -2607,24 +2554,26 @@
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: preliminary diligence and management meetings in June; fuller diligence materials only after 07/20. Updated IOI, up from $41.00–$43.00 (#20).</t>
+          <t>Unclear: subject to unspecified adjustments; earlier interest was subject to further diligence. Proposes to buy a portion of the CST business for $330 million (total, not per share).</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $45.00, Party H proposed $42.00 to $45.00, and Parent proposed $45.00” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="n"/>
+          <t>“Party G proposed acquiring a portion of Kraton’s CST business for $330 million, subject to adjustments.” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S31" s="2" t="n"/>
       <c r="T31" s="3" t="n">
-        <v>44396</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>44383</v>
-      </c>
+        <v>44379</v>
+      </c>
+      <c r="U31" s="2" t="n"/>
       <c r="V31" s="3" t="n">
-        <v>44396</v>
+        <v>44379</v>
       </c>
     </row>
     <row r="32">
@@ -2633,22 +2582,18 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>by 07/19/2021</t>
+          <t>07/06/2021</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kraton (target)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2657,52 +2602,38 @@
       <c r="G32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H32" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: preliminary diligence and management meetings in June; fuller diligence materials only after 07/20. Updated IOI, up from $41.00 (#21).</t>
+          <t>Board, reviewing the four whole-company IOIs, tells Party A, Party H, Parent and Party I it requires updated IOIs ascribing greater value by 07/19 before choosing any second-round invitees. Filing prints 'July 19, 2020'; context shows 2021.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $45.00, Party H proposed $42.00 to $45.00, and Parent proposed $45.00” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="n"/>
+          <t>“the Board would require updated indications of interest to be received by July 19, 2020 that ascribed a greater value to Kraton” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="3" t="n">
-        <v>44396</v>
+        <v>44383</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>44383</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>44396</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="33">
@@ -2711,18 +2642,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>07/19/2021</t>
+          <t>07/06/2021</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n"/>
+          <t>Parties C, G and K</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2736,33 +2671,35 @@
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
+      <c r="M33" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Round-2 due date. A, H and Parent raised (#29–#31); Party I said it would not raise $40.00. Enforced: the next day the board chose the second-round set from bids in hand (#33).</t>
+          <t>Board decides not to ask Party C, Party G or Party K for revised segment proposals 'at this time'; their proposals kept for evaluation alongside updated whole-company proposals. Not an exit.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“By July 19, 2021, Kraton received updated indications of interest with respect to a potential acquisition of the entire Company” (p. 36)</t>
+          <t>“The Board also determined not to request that Party C, Party G, or Party K submit revised indications of interest regarding their proposals to acquire portions of” (p. 35)</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="3" t="n">
-        <v>44396</v>
+        <v>44383</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>44396</v>
+        <v>44383</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>44396</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="34">
@@ -2771,25 +2708,25 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>07/20/2021</t>
+          <t>07/06/2021</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
+          <t>Reuters (media)</t>
         </is>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
@@ -2801,28 +2738,24 @@
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Board admits Party A, Party H and Parent to the second round with more financial and diligence material (same access for all three; management meetings week of 08/09). Asks J.P. Morgan for segment-sale analysis; C, G, K bids kept under review.</t>
+          <t>Media report that Kraton hired J.P. Morgan for a potential sale. Ref: $31.65 close 07/02/2021 (last unaffected day); $36.37 close 07/06/2021; $34.51–$42.80 closes thereafter to signing.</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“the Board instructed representatives of J.P. Morgan and Kraton’s senior management to invite Party A, Party H, and Parent to the second round of the transaction process” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“Reuters published a report stating, among other matters, that Kraton had hired J.P. Morgan as its financial advisor to advise Kraton with respect to a potential sale of the company” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
       <c r="T34" s="3" t="n">
-        <v>44397</v>
+        <v>44383</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>44397</v>
+        <v>44383</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>44397</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="35">
@@ -2831,22 +2764,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>by 07/20/2021</t>
+          <t>after 07/06/2021</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Party I</t>
+          <t>5 strategic post-Reuters inquirers</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -2861,37 +2794,29 @@
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>Would not improve earlier offer</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Asked to raise $40.00 (#22), it said by 07/19 it would not. It is left out of the named second-round set (#33); the filing does not say it was told. Board decided after the bidder refused to raise.</t>
+          <t>Inbound inquiries to J.P. Morgan after the Reuters report; invited to sign an NDA and bid; all five declined NDAs and made no proposals, so never entered.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>“Party I stated that it was not willing to increase its proposed purchase price of $40.00 per share” (p. 36)</t>
+          <t>“J.P. Morgan received inbound inquiries from six additional parties, five of which were strategic acquirers, and one of which was a financial acquirer” (p. 35)</t>
         </is>
       </c>
       <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="3" t="n">
-        <v>44397</v>
-      </c>
-      <c r="U35" s="2" t="n"/>
-      <c r="V35" s="3" t="n">
-        <v>44397</v>
-      </c>
+        <v>44383</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>44383</v>
+      </c>
+      <c r="V35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2899,22 +2824,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>by 07/20/2021</t>
+          <t>after 07/06/2021</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Party J</t>
+          <t>Post-Reuters financial party</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -2931,35 +2856,27 @@
       <c r="M36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Left out of the named second-round set (#33). Its $38.00–$41.00 (#28) was below the others' $42.00–$45.00, and J said it would not go higher. Filing does not say J was told.</t>
+          <t>Inbound inquiry to J.P. Morgan after the Reuters report; invited to sign an NDA and submit a proposal.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“Party J also stated that it was not willing to increase its purchase price beyond this range.” (p. 36)</t>
+          <t>“J.P. Morgan received inbound inquiries from six additional parties, five of which were strategic acquirers, and one of which was a financial acquirer” (p. 35)</t>
         </is>
       </c>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="3" t="n">
-        <v>44397</v>
-      </c>
-      <c r="U36" s="2" t="n"/>
-      <c r="V36" s="3" t="n">
-        <v>44397</v>
-      </c>
+        <v>44383</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>44383</v>
+      </c>
+      <c r="V36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2967,29 +2884,29 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/04/2021</t>
+          <t>after 07/06/2021</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Party G</t>
+          <t>Post-Reuters financial party</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
@@ -2999,37 +2916,31 @@
       <c r="M37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>No longer interested in the CST business; its $330 million bid (#14) lapses. Bidder decided.</t>
+          <t>Late entrant signs an NDA (11th confidentiality agreement in the process). Execution date not stated.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“On August 4, 2021, Party G informed Kraton that it was no longer interested in acquiring Kraton’s CST business.” (p. 36)</t>
+          <t>“Of these six parties, one party, a financial acquirer, executed a confidentiality agreement with Kraton” (p. 35)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="3" t="n">
-        <v>44412</v>
+        <v>44383</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>44412</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>44412</v>
-      </c>
+        <v>44383</v>
+      </c>
+      <c r="V37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -3037,59 +2948,63 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>after 08/11/2021</t>
+          <t>after 07/06/2021</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n"/>
+          <t>Post-Reuters financial party</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
+      <c r="M38" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Final bid procedures letter to A, H and Parent asks for merger-agreement markups by 09/08/2021 and final IOIs by 09/15/2021; draft merger agreement authorized 08/11. Narrated between 08/11 meeting and 08/13 reports.</t>
+          <t>Catch-up access: Kraton holds a preliminary management meeting with the late entrant, the access first-round NDA signers had in June. Date not stated.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“provided a final bid procedures letter to Party A, Party H, and Parent that requested these bidders to submit markups of a draft merger agreement by September 8, 2021” (p. 37)</t>
+          <t>“executed a confidentiality agreement with Kraton and participated in a preliminary management meeting with Kraton’s senior” (p. 35)</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="3" t="n">
-        <v>44420</v>
+        <v>44383</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>44419</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>44421</v>
-      </c>
+        <v>44383</v>
+      </c>
+      <c r="V38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3097,25 +3012,25 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>08/13/2021 and 08/16/2021</t>
+          <t>07/19/2021</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
+          <t>Kraton (target)</t>
         </is>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
@@ -3127,24 +3042,28 @@
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Media rumour: two outlets (08/13 and 08/16) report that potential acquirers were invited to a second round.</t>
+          <t>Due date for updated IOIs from the four whole-company bidders; responses received by 07/19/2021.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“two media outlets each published a report stating, among other matters, that potential acquirers of Kraton had been invited to the second round of a transaction process” (p. 37)</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="n"/>
+          <t>“By July 19, 2021, Kraton received updated indications of interest with respect to a potential acquisition of the entire Company” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="3" t="n">
-        <v>44421</v>
+        <v>44396</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>44421</v>
+        <v>44396</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>44424</v>
+        <v>44396</v>
       </c>
     </row>
     <row r="40">
@@ -3153,12 +3072,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>after 07/06/2021</t>
+          <t>by 07/19/2021</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>5 strategic inbound parties (post-Reuters)</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3168,7 +3087,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -3177,40 +3096,52 @@
       <c r="G40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
+      <c r="H40" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Inbound inquiries after the Reuters report (#27) about the review process; invited to sign an NDA and bid, all five declined and never entered. Only bound: after 07/06, before signing; sorted at window midpoint.</t>
+          <t>No conditions stated; second-round diligence not yet opened. Updated IOI at $45.00, up from $42.00–$45.00 (#21).</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“J.P. Morgan received inbound inquiries from six additional parties, five of which were strategic acquirers, and one of which was a financial acquirer” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>“Party A proposed $45.00, Party H proposed $42.00 to $45.00, and Parent proposed $45.00.” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="n"/>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="3" t="n">
-        <v>44424</v>
+        <v>44396</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>44383</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>44466</v>
+        <v>44396</v>
       </c>
     </row>
     <row r="41">
@@ -3219,12 +3150,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>after 07/06/2021</t>
+          <t>by 07/19/2021</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Unnamed post-Reuters financial party</t>
+          <t>Party H</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3234,7 +3165,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -3243,11 +3174,27 @@
       <c r="G41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
+      <c r="H41" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="n">
         <v>1</v>
       </c>
@@ -3255,28 +3202,24 @@
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Sixth post-Reuters inbound inquiry; invited to sign an NDA and bid. Undated beyond 07/06–signing; sorted at window midpoint.</t>
+          <t>No conditions stated; second-round diligence not yet opened. Updated IOI at $42.00–$45.00, up from $41.00–$43.00 (#22).</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“J.P. Morgan received inbound inquiries from six additional parties, five of which were strategic acquirers, and one of which was a financial acquirer” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>“Party A proposed $45.00, Party H proposed $42.00 to $45.00, and Parent proposed $45.00.” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="3" t="n">
-        <v>44424</v>
+        <v>44396</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>44383</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>44466</v>
+        <v>44396</v>
       </c>
     </row>
     <row r="42">
@@ -3285,22 +3228,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>after 07/06/2021</t>
+          <t>by 07/19/2021</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Unnamed post-Reuters financial party</t>
+          <t>Parent (DL Chemical)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -3309,11 +3252,27 @@
       <c r="G42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="n"/>
+      <c r="H42" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="n">
         <v>1</v>
       </c>
@@ -3321,28 +3280,24 @@
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Entry. Signed an NDA and got a catch-up preliminary management meeting; eleventh NDA party (outside the 10 in #11/#12). Undated; sorted at window midpoint.</t>
+          <t>No conditions stated; second-round diligence not yet opened. Updated IOI at $45.00, up from $41.00 (#23).</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“one party, a financial acquirer, executed a confidentiality agreement with Kraton and participated in a preliminary management meeting” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>“Party A proposed $45.00, Party H proposed $42.00 to $45.00, and Parent proposed $45.00.” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="3" t="n">
-        <v>44424</v>
+        <v>44396</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>44383</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>44466</v>
+        <v>44396</v>
       </c>
     </row>
     <row r="43">
@@ -3351,12 +3306,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>08/20/2021</t>
+          <t>by 07/19/2021</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Party H</t>
+          <t>Party I</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3366,14 +3321,14 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
@@ -3383,32 +3338,32 @@
       <c r="M43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>Value below earlier offer</t>
-        </is>
-      </c>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Says it cannot maintain its $42.00–$45.00 range (#30) and cannot continue; left before markups were due. Bidder decided.</t>
+          <t>Party I answers the request for greater value by refusing to raise its $40.00 (#24); no new bid.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“Party H informed Kraton that it was unable to maintain its indicative bid price range and was unable to continue in the process.” (p. 37)</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="n"/>
+          <t>“Party I stated that it was not willing to increase its proposed purchase price of $40.00 per share.” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="3" t="n">
-        <v>44428</v>
+        <v>44396</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>44428</v>
+        <v>44383</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>44428</v>
+        <v>44396</v>
       </c>
     </row>
     <row r="44">
@@ -3417,12 +3372,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>08/30/2021</t>
+          <t>by 07/19/2021</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Party K</t>
+          <t>Party J</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3432,14 +3387,14 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
@@ -3453,24 +3408,26 @@
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Target requests an updated chemical-segment proposal from Party K, although board finds Sum of the Parts (best case ~$44–$51/share, 08/22) unlikely to beat a whole-company sale. Party C's CST bid still standing.</t>
+          <t>Party J returns after not submitting in round 1 (#25), with its announced mid-July bid; not among the four asked for updated IOIs, so received but not admitted.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“the Board therefore instructed J.P. Morgan to request an updated proposal from Party K regarding its possible acquisition of Kraton’s chemical segment” (p. 38)</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="n"/>
+          <t>“Party J also submitted an indication of interest that proposed an acquisition of Kraton at a per share purchase price of $38.00 to $41.00 per share.” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="3" t="n">
-        <v>44438</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>44438</v>
-      </c>
+        <v>44396</v>
+      </c>
+      <c r="U44" s="2" t="n"/>
       <c r="V44" s="3" t="n">
-        <v>44438</v>
+        <v>44396</v>
       </c>
     </row>
     <row r="45">
@@ -3479,42 +3436,64 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>09/08/2021</t>
+          <t>by 07/19/2021</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
+          <t>Party J</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Markup due date. Parent and Party A submit markups (H already out). Parent: deletes hell-or-high-water, 3.5%-of-EV company fee, no financing condition but debt-funded with a delayed marketing period. Passed without action: bidding continued to 09/15.</t>
+          <t>No conditions stated; diligence open. First IOI, $38.00–$41.00, and J said it would not go above this range. Unsolicited in round 2.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“On September 8, 2021, Parent and Party A submitted their markups of the draft merger agreement.” (p. 38)</t>
+          <t>“Party J also submitted an indication of interest that proposed an acquisition of Kraton at a per share purchase price of $38.00 to $41.00 per share.” (p. 36)</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -3524,13 +3503,11 @@
       </c>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>44447</v>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>44447</v>
-      </c>
+        <v>44396</v>
+      </c>
+      <c r="U45" s="2" t="n"/>
       <c r="V45" s="3" t="n">
-        <v>44447</v>
+        <v>44396</v>
       </c>
     </row>
     <row r="46">
@@ -3539,22 +3516,18 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>09/09/2021</t>
+          <t>07/20/2021</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Party K</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kraton (target)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3565,50 +3538,36 @@
       </c>
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
       <c r="N46" s="2" t="n"/>
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Subject to further diligence and price adjustments; no debt financing talks and no equity arrangements. Chemical segment at 9.5x trailing-12-month adjusted EBITDA to Sept 2021; K puts EV at $1.25 billion. Answers #43.</t>
+          <t>Board selects Party A, Party H and Parent for the filing's 'second round' and gives all three additional financial and diligence materials; diligence management meetings week of 08/09/2021. No bid due date yet. Board also asks for analysis of separate segment sales.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>“Party K submitted an updated indication of interest whereby it proposed to acquire Kraton’s chemical segment for a purchase price equal to 9.5x the adjusted EBITDA” (p. 38)</t>
+          <t>“the Board instructed representatives of J.P. Morgan and Kraton’s senior management to invite Party A, Party H, and Parent to the second round of the transaction process” (p. 36)</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>44448</v>
+        <v>44397</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>44448</v>
+        <v>44397</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>44448</v>
+        <v>44397</v>
       </c>
     </row>
     <row r="47">
@@ -3617,64 +3576,56 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>09/15/2021</t>
+          <t>07/20/2021</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
+          <t>Party I</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Would not improve earlier offer</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Substantially all diligence done; its 09/08 markup (#44) drops any financing condition but needs debt financing. On-time final-round bid; Formal (markup plus final solicitation).</t>
+          <t>Not in the named advancing set (#45). Party I had been asked for greater value and refused to raise $40.00 (#42).</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>“On September 15, 2021, Parent provided a revised proposal to acquire Kraton for $46.00 per share. Parent noted that it had completed substantially all due diligence.” (p. 39)</t>
+          <t>“the Board instructed representatives of J.P. Morgan and Kraton’s senior management to invite Party A, Party H, and Parent to the second round of the transaction process” (p. 36)</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
@@ -3684,13 +3635,13 @@
       </c>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="3" t="n">
-        <v>44454</v>
+        <v>44397</v>
       </c>
       <c r="U47" s="3" t="n">
-        <v>44454</v>
+        <v>44397</v>
       </c>
       <c r="V47" s="3" t="n">
-        <v>44454</v>
+        <v>44397</v>
       </c>
     </row>
     <row r="48">
@@ -3699,42 +3650,56 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/15/2021</t>
+          <t>07/20/2021</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n"/>
+          <t>Party J</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n"/>
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
-      <c r="M48" s="2" t="n"/>
-      <c r="N48" s="2" t="n"/>
-      <c r="O48" s="2" t="n"/>
+      <c r="M48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Final-IOI due date. Parent bid on time (#46); Party A bid on 09/17 (#48), and the board considered it on 09/18 — late bid accepted.</t>
+          <t>Not in the named advancing set (#45); its $38.00–$41.00 was below the other three bids. J was not asked to improve.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>“and final indications of interest by September 15, 2021” (p. 37)</t>
+          <t>“the Board instructed representatives of J.P. Morgan and Kraton’s senior management to invite Party A, Party H, and Parent to the second round of the transaction process” (p. 36)</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
@@ -3744,13 +3709,13 @@
       </c>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="3" t="n">
-        <v>44454</v>
+        <v>44397</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>44454</v>
+        <v>44397</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>44454</v>
+        <v>44397</v>
       </c>
     </row>
     <row r="49">
@@ -3759,12 +3724,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/17/2021</t>
+          <t>08/04/2021</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Party G</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3774,7 +3739,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
@@ -3783,56 +3748,44 @@
       <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="4" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Subject to additional due diligence (not called confirmatory). Late final-round bid backed by its 09/08 markup; price down from $45.00 (#29). Alternative structure in #49.</t>
+          <t>CST-only bidder (#30): no longer interested in acquiring the CST business.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>“On September 17, 2021, Party A provided a revised proposal to acquire Kraton for $40.50 per share.” (p. 39)</t>
+          <t>“On August 4, 2021, Party G informed Kraton that it was no longer interested in acquiring Kraton’s CST business.” (p. 36)</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>Q5; Q8</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="3" t="n">
-        <v>44456</v>
+        <v>44412</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>44456</v>
+        <v>44412</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>44456</v>
+        <v>44412</v>
       </c>
     </row>
     <row r="50">
@@ -3841,22 +3794,18 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>09/17/2021</t>
+          <t>08/13/2021</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Media outlet 1</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
@@ -3867,50 +3816,32 @@
       </c>
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
       <c r="N50" s="2" t="n"/>
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Subject to additional diligence and adjustments. Alternative to #48: buy the polymer segment for $1.3 billion EV and spin off the chemical business to Kraton holders; no per-share figure. Informal: outside the markup's whole-company scope.</t>
+          <t>Media report that potential acquirers had been invited to a second round.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>“Party A also proposed an alternative transaction whereby it would acquire Kraton’s polymer segment for an enterprise value equal to $1.3 billion, subject to certain adjustments” (p. 39)</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>Q4; Q8</t>
-        </is>
-      </c>
+          <t>“On August 13 and August 16, 2021, two media outlets each published a report stating, among other matters, that potential acquirers of Kraton had been invited to the second round” (p. 37)</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="3" t="n">
-        <v>44456</v>
+        <v>44421</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>44456</v>
+        <v>44421</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>44456</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="51">
@@ -3919,25 +3850,25 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>09/18/2021</t>
+          <t>after 08/11/2021, by 08/20/2021</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
+          <t>Kraton (target)</t>
         </is>
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
@@ -3949,24 +3880,28 @@
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Target sets price requirement: asks Parent for $46.50 and a reverse fee for debt-financing failure; tells Party A its bid is inadequate. Board again rejects Sum of the Parts (best case ~$46–$48/share using #45 and #49).</t>
+          <t>Final bid procedures letter to Party A, Party H and Parent: merger agreement markups due 09/08/2021, final IOIs due 09/15/2021; Board authorized sending the draft merger agreement 08/11. Date to 08/20 inferred: Party H received the letter and quit that day.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>“the Board instructed J.P. Morgan to request that Parent increase its proposal to $46.50 per share, and to also inform Party A that its proposal did not provide adequate value” (p. 39)</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="n"/>
+          <t>“a final bid procedures letter to Party A, Party H, and Parent that requested these bidders to submit markups of a draft merger agreement by September 8, 2021” (p. 37)</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="3" t="n">
-        <v>44457</v>
+        <v>44423</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>44457</v>
+        <v>44419</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>44457</v>
+        <v>44428</v>
       </c>
     </row>
     <row r="52">
@@ -3975,80 +3910,54 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>09/20/2021</t>
+          <t>08/16/2021</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Media outlet 2</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="I52" s="4" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n"/>
       <c r="N52" s="2" t="n"/>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Substantially all diligence done (#46); debt commitment letter still in draft. Best and final, meeting the 09/18 ask (#50). Cash per p.42 ('final price of $46.50 in cash').</t>
+          <t>Second media report that potential acquirers had been invited to a second round.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>“Parent would increase its purchase price to $46.50 per share, and that this proposal was its best and final offer” (p. 39)</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
+          <t>“On August 13 and August 16, 2021, two media outlets each published a report stating, among other matters, that potential acquirers of Kraton had been invited to the second round” (p. 37)</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="3" t="n">
-        <v>44459</v>
+        <v>44424</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>44459</v>
+        <v>44424</v>
       </c>
       <c r="V52" s="3" t="n">
-        <v>44459</v>
+        <v>44424</v>
       </c>
     </row>
     <row r="53">
@@ -4057,54 +3966,64 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>09/20/2021</t>
+          <t>08/20/2021</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>O’Melveny &amp; Myers LLP</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n"/>
+          <t>Party H</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
       <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n"/>
-      <c r="N53" s="2" t="n"/>
+      <c r="M53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Value below earlier offer</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Parent's legal counsel; first seen acting 09/20/2021, receiving Kraton's revised merger agreement and negotiating it through 09/26.</t>
+          <t>Party H said it could not maintain its $42.00–$45.00 indicative range (#40) and could not continue, implying value below its earlier offer.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>“O’Melveny &amp; Myers LLP, as counsel to Parent” (p. 39)</t>
+          <t>“Party H informed Kraton that it was unable to maintain its indicative bid price range and was unable to continue in the process.” (p. 37)</t>
         </is>
       </c>
       <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="3" t="n">
-        <v>44459</v>
+        <v>44428</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>44459</v>
+        <v>44428</v>
       </c>
       <c r="V53" s="3" t="n">
-        <v>44459</v>
+        <v>44428</v>
       </c>
     </row>
     <row r="54">
@@ -4113,19 +4032,15 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>09/20/2021</t>
+          <t>08/30/2021</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kraton (target)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -4135,38 +4050,36 @@
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
-      <c r="M54" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M54" s="2" t="n"/>
       <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Target moves to finalize with Parent: King &amp; Spalding sends revised merger agreement (3% company fee, 7% reverse fee) and debt commitment draft; negotiated 09/20–09/26 to $63 million each way. No exclusivity reported; Party A still bidding.</t>
+          <t>After 08/22 and 08/30 Sum of the Parts reviews, Board finds separate segment sales unlikely to beat a whole-company sale but keeps alternatives open; asks J.P. Morgan to request an updated proposal from Party K.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>“Following Parent’s confirmation that it would increase its purchase price, King &amp; Spalding LLP provided a revised draft of the merger agreement to O’Melveny &amp; Myers LLP” (p. 39)</t>
+          <t>“the Board therefore instructed J.P. Morgan to request an updated proposal from Party K regarding its possible acquisition of Kraton’s chemical segment” (p. 38)</t>
         </is>
       </c>
       <c r="R54" s="2" t="n"/>
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="3" t="n">
-        <v>44459</v>
+        <v>44438</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>44459</v>
+        <v>44438</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>44459</v>
+        <v>44438</v>
       </c>
     </row>
     <row r="55">
@@ -4175,12 +4088,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>09/21/2021</t>
+          <t>09/08/2021</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Parent (DL Chemical)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -4190,36 +4103,20 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="n"/>
       <c r="M55" s="2" t="n">
         <v>1</v>
       </c>
@@ -4227,12 +4124,12 @@
       <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: 'additional' diligence on 09/17 (#48); on 09/24 it 'remained subject to confirmatory' diligence. $42.00 plus earnout if the chemical segment later sells above thresholds (amount unstated).</t>
+          <t>Parent submits merger agreement markup, no new price: deletes hell-or-high-water; company termination fee 3.5% of enterprise value (vs 2% equity); no financing condition, but delayed debt marketing period and specific performance/damages as sole recourse on financing failure.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>“Party A submitted an updated proposal in which it proposed to acquire Kraton for $42.00 per share, with an “earnout” structure” (p. 40)</t>
+          <t>“On September 8, 2021, Parent and Party A submitted their markups of the draft merger agreement.” (p. 38)</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
@@ -4242,13 +4139,13 @@
       </c>
       <c r="S55" s="2" t="n"/>
       <c r="T55" s="3" t="n">
-        <v>44460</v>
+        <v>44447</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>44460</v>
+        <v>44447</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>44460</v>
+        <v>44447</v>
       </c>
     </row>
     <row r="56">
@@ -4257,7 +4154,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>09/24/2021</t>
+          <t>09/08/2021</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4272,36 +4169,20 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n">
         <v>1</v>
       </c>
@@ -4309,24 +4190,28 @@
       <c r="O56" s="2" t="n"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Confirmatory diligence only. $44.00 plus earnout: holders get 50% of net chemical-sale proceeds above thresholds if a sale is signed before closing. Best and final; follows board's 09/23 'inadequate' message.</t>
+          <t>Party A submits its merger agreement markup on the markup due date, no new price; contents not described.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>“Party A stated that this proposal was its best and final offer and that it remained subject to confirmatory due diligence.” (p. 40)</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="n"/>
+          <t>“On September 8, 2021, Parent and Party A submitted their markups of the draft merger agreement.” (p. 38)</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
       <c r="S56" s="2" t="n"/>
       <c r="T56" s="3" t="n">
-        <v>44463</v>
+        <v>44447</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>44463</v>
+        <v>44447</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>44463</v>
+        <v>44447</v>
       </c>
     </row>
     <row r="57">
@@ -4335,52 +4220,76 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>by 09/27/2021</t>
+          <t>09/09/2021</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs (Asia) L.L.C., Seoul Branch</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="n"/>
+          <t>Party K</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n"/>
-      <c r="J57" s="2" t="n"/>
-      <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="n"/>
-      <c r="M57" s="2" t="n"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N57" s="2" t="n"/>
       <c r="O57" s="2" t="n"/>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Parent's investment banker (the only broker/adviser Parent retained, per merger agreement rep, p.68); first seen at signing, role not described. Affiliate Goldman Sachs Bank USA gave Parent's debt commitment (lender, no row).</t>
+          <t>Heavy: subject to further diligence and price adjustments; no debt financing talks and no equity financing arrangements. Requested update (#53): chemical segment at 9.5x trailing-12-month (Sept 2021) segment adjusted EBITDA, purported enterprise value $1.25 billion.</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>“other than those payable to Goldman Sachs (Asia) L.L.C., Seoul Branch” (p. 68)</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="n"/>
+          <t>“Party K submitted an updated indication of interest whereby it proposed to acquire Kraton’s chemical segment for a purchase price equal to 9.5x the adjusted EBITDA” (p. 38)</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S57" s="2" t="n"/>
       <c r="T57" s="3" t="n">
-        <v>44466</v>
-      </c>
-      <c r="U57" s="2" t="n"/>
+        <v>44448</v>
+      </c>
+      <c r="U57" s="3" t="n">
+        <v>44448</v>
+      </c>
       <c r="V57" s="3" t="n">
-        <v>44466</v>
+        <v>44448</v>
       </c>
     </row>
     <row r="58">
@@ -4389,60 +4298,58 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/27/2021</t>
+          <t>09/15/2021</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kraton (target)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
       <c r="J58" s="2" t="n"/>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M58" s="2" t="n"/>
       <c r="N58" s="2" t="n"/>
       <c r="O58" s="2" t="n"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>$46.50 cash per share. Board approved 09/26 after J.P. Morgan's fairness opinion. $63 million company fee and $63 million reverse fee for debt-financing failure; no financing condition; Goldman Sachs Bank USA commits up to $1.75 billion debt.</t>
+          <t>Due date for final indications of interest (markups were due 09/08/2021). Parent bid on the day; Party A bid on 09/17/2021 and the Board reviewed it 09/18/2021.</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>“Kraton, Parent, Merger Subsidiary and Intermediate Merger Subsidiary entered into the Merger Agreement” (p. 41)</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="n"/>
+          <t>“and final indications of interest by September 15, 2021” (p. 37)</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S58" s="2" t="n"/>
       <c r="T58" s="3" t="n">
-        <v>44466</v>
+        <v>44454</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>44466</v>
+        <v>44454</v>
       </c>
       <c r="V58" s="3" t="n">
-        <v>44466</v>
+        <v>44454</v>
       </c>
     </row>
     <row r="59">
@@ -4451,56 +4358,80 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/27/2021</t>
+          <t>09/15/2021</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Kraton</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n"/>
+          <t>Parent (DL Chemical)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="n"/>
-      <c r="I59" s="2" t="n"/>
-      <c r="J59" s="2" t="n"/>
-      <c r="K59" s="2" t="n"/>
-      <c r="L59" s="2" t="n"/>
-      <c r="M59" s="2" t="n"/>
+      <c r="G59" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Kraton and Parent issue press releases before the market opens.</t>
+          <t>Light: Parent says it has completed substantially all due diligence; financing not a condition (markup #54). Formal: markup plus response to final-bid letter. $46.00 per share, up from $45.00 (#41).</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>“Kraton and Parent issued press releases announcing execution of the Merger Agreement.” (p. 41)</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="n"/>
+          <t>“On September 15, 2021, Parent provided a revised proposal to acquire Kraton for $46.00 per share. Parent noted that it had completed substantially all due diligence.” (p. 39)</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
       <c r="S59" s="2" t="n"/>
       <c r="T59" s="3" t="n">
-        <v>44466</v>
+        <v>44454</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>44466</v>
+        <v>44454</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>44466</v>
+        <v>44454</v>
       </c>
     </row>
     <row r="60">
@@ -4509,7 +4440,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>09/27/2021</t>
+          <t>09/17/2021</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4524,49 +4455,65 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" s="2" t="n"/>
-      <c r="I60" s="2" t="n"/>
-      <c r="J60" s="2" t="n"/>
-      <c r="K60" s="2" t="n"/>
-      <c r="L60" s="2" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M60" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
+      <c r="N60" s="2" t="n"/>
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Board found on 09/26 that A's $44.00 plus earnout (#55) was not likely to beat Parent's $46.50, citing earnout, complexity, timing and regulatory risk. Target decided.</t>
+          <t>Heavy: 'subject to additional due diligence'. Formal: markup (#55) plus final-round response, two days after the 09/15 due date. $40.50 per share, down from $45.00 (#39).</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>“the Board determined that Party A’s proposal was not reasonably likely to deliver greater value to Kraton’s stockholders relative to the proposal from Parent” (p. 40)</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="n"/>
+          <t>“On September 17, 2021, Party A provided a revised proposal to acquire Kraton for $40.50 per share.” (p. 39)</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>Q4; Q9</t>
+        </is>
+      </c>
       <c r="S60" s="2" t="n"/>
       <c r="T60" s="3" t="n">
-        <v>44466</v>
+        <v>44456</v>
       </c>
       <c r="U60" s="3" t="n">
-        <v>44466</v>
+        <v>44456</v>
       </c>
       <c r="V60" s="3" t="n">
-        <v>44466</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="61">
@@ -4575,12 +4522,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>09/27/2021</t>
+          <t>09/17/2021</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Party K</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4590,49 +4537,57 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="n"/>
-      <c r="J61" s="2" t="n"/>
-      <c r="K61" s="2" t="n"/>
-      <c r="L61" s="2" t="n"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M61" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason</t>
-        </is>
-      </c>
+      <c r="N61" s="2" t="n"/>
       <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Chemical-segment bid (#45) still standing; on 09/18 the board judged a Sum of the Parts built on it no better than a whole-company sale, and it signed with Parent. Target decided.</t>
+          <t>Heavy: subject to additional due diligence and adjustments. Alternative to #59: buys the polymer segment at $1.3 billion enterprise value while the chemical business is spun off to Kraton stockholders.</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>“again determined that a Sum of the Parts Strategy was not likely to deliver greater value for Kraton’s stockholders” (p. 39)</t>
+          <t>“Party A also proposed an alternative transaction whereby it would acquire Kraton’s polymer segment for an enterprise value equal to $1.3 billion, subject to certain adjustments” (p. 39)</t>
         </is>
       </c>
       <c r="R61" s="2" t="n"/>
       <c r="S61" s="2" t="n"/>
       <c r="T61" s="3" t="n">
-        <v>44466</v>
+        <v>44456</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>44466</v>
+        <v>44456</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>44466</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="62">
@@ -4641,12 +4596,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>by 09/27/2021</t>
+          <t>09/18/2021</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Parent (DL Chemical)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4656,14 +4611,14 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="n"/>
@@ -4673,40 +4628,28 @@
       <c r="M62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N62" s="2" t="n"/>
+      <c r="O62" s="2" t="n"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>CST bid of $100 million (#13) last reported standing 08/30 (the only other non-withdrawn chemical-side proposal); never mentioned again. Closed at signing.</t>
+          <t>Price requirement: Board asks Parent to raise to $46.50 and says Kraton expects a reverse break fee on debt financing failure. Board again rejects Sum of the Parts (updated best case about $46–$48 per share).</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>“segment was from Party C , which proposed acquiring Kraton’s CST business for $100 million.” (p. 38)</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>“the Board instructed J.P. Morgan to request that Parent increase its proposal to $46.50 per share, and to also inform Party A that its proposal did not provide adequate value” (p. 39)</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="n"/>
       <c r="S62" s="2" t="n"/>
       <c r="T62" s="3" t="n">
-        <v>44466</v>
+        <v>44457</v>
       </c>
       <c r="U62" s="3" t="n">
-        <v>44438</v>
+        <v>44457</v>
       </c>
       <c r="V62" s="3" t="n">
-        <v>44466</v>
+        <v>44457</v>
       </c>
     </row>
     <row r="63">
@@ -4715,29 +4658,29 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>by 09/27/2021</t>
+          <t>09/18/2021</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Unnamed post-Reuters financial party</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
@@ -4747,42 +4690,840 @@
       <c r="M63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="n"/>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Filing reports it signed an NDA (#41) and met management but never submitted a proposal; when it stopped is not stated, so closed at signing.</t>
+          <t>Board tells Party A its $40.50 proposal (#59) does not offer adequate value; Party A stays in.</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>“management but did not submit any proposal with respect to a transaction” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>“and to also inform Party A that its proposal did not provide adequate value to Kraton and its stockholders.” (p. 39)</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="n"/>
       <c r="S63" s="2" t="n"/>
       <c r="T63" s="3" t="n">
+        <v>44457</v>
+      </c>
+      <c r="U63" s="3" t="n">
+        <v>44457</v>
+      </c>
+      <c r="V63" s="3" t="n">
+        <v>44457</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>09/20/2021</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Parent (DL Chemical)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="n"/>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>Light: diligence substantially complete (#58); only final documentation remained, negotiated 09/20–09/26 (termination fees settled at $63 million each way). Formal. Raises to the requested $46.50 per share, stated as best and final.</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>“Parent would increase its purchase price to $46.50 per share, and that this proposal was its best and final offer.” (p. 39)</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="n"/>
+      <c r="S64" s="2" t="n"/>
+      <c r="T64" s="3" t="n">
+        <v>44459</v>
+      </c>
+      <c r="U64" s="3" t="n">
+        <v>44459</v>
+      </c>
+      <c r="V64" s="3" t="n">
+        <v>44459</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>09/20/2021</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>O’Melveny &amp; Myers LLP (Parent)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Adviser</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="n"/>
+      <c r="M65" s="2" t="n"/>
+      <c r="N65" s="2" t="n"/>
+      <c r="O65" s="2" t="n"/>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>Parent's legal counsel; first shown acting 09/20/2021, when it received King &amp; Spalding's revised merger agreement draft.</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>“O’Melveny &amp; Myers LLP, as counsel to Parent” (p. 39)</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="n"/>
+      <c r="S65" s="2" t="n"/>
+      <c r="T65" s="3" t="n">
+        <v>44459</v>
+      </c>
+      <c r="U65" s="3" t="n">
+        <v>44459</v>
+      </c>
+      <c r="V65" s="3" t="n">
+        <v>44459</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>09/21/2021</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="2" t="n"/>
+      <c r="O66" s="2" t="n"/>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>Unclear: no condition stated, but Party A's diligence was still open (#59, #67). Formal (markup on file). $42.00 per share plus an earnout paid if the chemical segment is sold above thresholds; Price low only.</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>“Party A submitted an updated proposal in which it proposed to acquire Kraton for $42.00 per share, with an “earnout” structure” (p. 40)</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="n"/>
+      <c r="T66" s="3" t="n">
+        <v>44460</v>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>44460</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>44460</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>09/23/2021</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Other material event</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" s="2" t="n"/>
+      <c r="M67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" s="2" t="n"/>
+      <c r="O67" s="2" t="n"/>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>Board, citing risks and contingencies and stockholders not sharing fully in chemical-sale value under the earnout, tells Party A its proposal (#65) does not offer adequate value.</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>“the Board instructed J.P. Morgan to inform Party A that its proposal did not provide adequate value to Kraton and its stockholders.” (p. 40)</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="n"/>
+      <c r="S67" s="2" t="n"/>
+      <c r="T67" s="3" t="n">
+        <v>44462</v>
+      </c>
+      <c r="U67" s="3" t="n">
+        <v>44462</v>
+      </c>
+      <c r="V67" s="3" t="n">
+        <v>44462</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>09/24/2021</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" s="2" t="n"/>
+      <c r="O68" s="2" t="n"/>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Light: only confirmatory due diligence. Formal; stated best and final. $44.00 per share plus revised earnout: 50% of net proceeds above thresholds if Kraton agrees to sell the chemical business before closing. Price low only.</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>“On September 24, 2021, Party A submitted an updated proposal whereby it would acquire Kraton for $44.00 per share.” (p. 40)</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="n"/>
+      <c r="S68" s="2" t="n"/>
+      <c r="T68" s="3" t="n">
+        <v>44463</v>
+      </c>
+      <c r="U68" s="3" t="n">
+        <v>44463</v>
+      </c>
+      <c r="V68" s="3" t="n">
+        <v>44463</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>by 09/27/2021</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs (Asia) L.L.C., Seoul Branch (Parent)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Adviser</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="n"/>
+      <c r="J69" s="2" t="n"/>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="n"/>
+      <c r="N69" s="2" t="n"/>
+      <c r="O69" s="2" t="n"/>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>Parent's investment banker/broker, from the merger agreement's fees representation (Annex A), not the background. Goldman Sachs Bank USA separately provided Parent's debt commitment (up to $1.75 billion).</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>“Except for Goldman Sachs (Asia) L.L.C., Seoul Branch, there is no investment banker, broker, finder or other intermediary that has been retained by” (p. A-37)</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="n"/>
+      <c r="S69" s="2" t="n"/>
+      <c r="T69" s="3" t="n">
         <v>44466</v>
       </c>
-      <c r="U63" s="2" t="n"/>
-      <c r="V63" s="3" t="n">
+      <c r="U69" s="2" t="n"/>
+      <c r="V69" s="3" t="n">
         <v>44466</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>09/27/2021</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Parent (DL Chemical)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Merger agreement signed</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2" t="n"/>
+      <c r="J70" s="2" t="n"/>
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" s="2" t="n"/>
+      <c r="M70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" s="2" t="n"/>
+      <c r="O70" s="2" t="n"/>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>$46.50 per share in cash. Board approved 09/26 after J.P. Morgan's fairness opinion. $63 million company termination fee (~4% of equity value); $63 million reverse fee on debt financing failure; no financing condition.</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>“Kraton, Parent, Merger Subsidiary and Intermediate Merger Subsidiary entered into the Merger Agreement” (p. 41)</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="n"/>
+      <c r="S70" s="2" t="n"/>
+      <c r="T70" s="3" t="n">
+        <v>44466</v>
+      </c>
+      <c r="U70" s="3" t="n">
+        <v>44466</v>
+      </c>
+      <c r="V70" s="3" t="n">
+        <v>44466</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>09/27/2021</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Not selected at signing</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="n"/>
+      <c r="J71" s="2" t="n"/>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="n"/>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>Board on 09/26 judged Party A's $44.00-plus-earnout proposal (#67), given its complexity, timing and regulatory risks, not reasonably likely to deliver more value than Parent's.</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>“the Board determined that Party A’s proposal was not reasonably likely to deliver greater value to Kraton’s stockholders relative to the proposal from Parent.” (p. 40)</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="n"/>
+      <c r="S71" s="2" t="n"/>
+      <c r="T71" s="3" t="n">
+        <v>44466</v>
+      </c>
+      <c r="U71" s="3" t="n">
+        <v>44466</v>
+      </c>
+      <c r="V71" s="3" t="n">
+        <v>44466</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>by 09/27/2021</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Party K</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Not selected at signing</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Chemical-segment proposal (#56) still outstanding at signing; the Board had rejected a Sum of the Parts strategy built partly on it. No reported withdrawal.</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>“again determined that a Sum of the Parts Strategy was not likely to deliver greater value for Kraton’s stockholders as compared to what could be achieved” (p. 39)</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="n"/>
+      <c r="T72" s="3" t="n">
+        <v>44466</v>
+      </c>
+      <c r="U72" s="2" t="n"/>
+      <c r="V72" s="3" t="n">
+        <v>44466</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>by 09/27/2021</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Not selected at signing</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="2" t="n"/>
+      <c r="L73" s="2" t="n"/>
+      <c r="M73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>Party C's $100 million CST proposal (#29) was described as non-withdrawn on 08/30/2021 and never mentioned again; still open at signing.</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>“the only other non-withdrawn proposal Kraton had received regarding its chemical” (p. 37)</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="n"/>
+      <c r="T73" s="3" t="n">
+        <v>44466</v>
+      </c>
+      <c r="U73" s="2" t="n"/>
+      <c r="V73" s="3" t="n">
+        <v>44466</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>by 09/27/2021</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Post-Reuters financial party</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Did not submit</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H74" s="2" t="n"/>
+      <c r="I74" s="2" t="n"/>
+      <c r="J74" s="2" t="n"/>
+      <c r="K74" s="2" t="n"/>
+      <c r="L74" s="2" t="n"/>
+      <c r="M74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>The filing reports it never submitted a proposal; it was invited to bid (#35) but not included in the 07/20 advancing set. Its exit timing is inferred as by signing, because its NDA date is unknown.</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>“management but did not submit any proposal with respect to a transaction.” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="n"/>
+      <c r="T74" s="3" t="n">
+        <v>44466</v>
+      </c>
+      <c r="U74" s="2" t="n"/>
+      <c r="V74" s="3" t="n">
+        <v>44466</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>09/27/2021</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Kraton (target)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Merger announced</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n"/>
+      <c r="I75" s="2" t="n"/>
+      <c r="J75" s="2" t="n"/>
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="2" t="n"/>
+      <c r="M75" s="2" t="n"/>
+      <c r="N75" s="2" t="n"/>
+      <c r="O75" s="2" t="n"/>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>Kraton and Parent issue press releases before the NYSE open.</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>“Kraton and Parent issued press releases announcing execution of the Merger Agreement.” (p. 41)</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="n"/>
+      <c r="S75" s="2" t="n"/>
+      <c r="T75" s="3" t="n">
+        <v>44466</v>
+      </c>
+      <c r="U75" s="3" t="n">
+        <v>44466</v>
+      </c>
+      <c r="V75" s="3" t="n">
+        <v>44466</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V63"/>
+  <autoFilter ref="A1:V75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4793,16 +5534,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
@@ -4872,12 +5613,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Board directed outreach to 14 listed buyers and a two-phase process; process letter asked NDA signers for initial IOIs</t>
+          <t>Board directs outreach to 14 listed buyers and launches the first round (two-phase design)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>10 NDA signers: 6 strategic (incl. inbound party; assumed Party A, Parent, Party J, Party K) and 4 financial (assumed Party H, Party I). CST-only, other-scope: Party C, D, E, G (strategic)</t>
+          <t>10 NDA signers: 6 strategic (incl. inbound party; presumed Party A, Parent, Party J, Party K) and 4 financial (presumed Party H, Party I). Segment track: Parties C, D, E, G (strategic, CST only).</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -4887,7 +5628,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Late bids accepted</t>
+          <t>Enforced</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -4897,12 +5638,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Whole company: 5 — Party A, Party H, Parent, Party I (by 07/02), Party J (late, 07/19). Other-scope: Party K (chemical segment), Party C and Party G (CST portions)</t>
+          <t>4 whole-company: Party A $42–45, Party H $41–43, Parent $41, Party I $40. Other-scope: Party K (chemical segment), Party C and Party G (CST portions).</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Four whole-company bidders asked for more value (round 2); 1 signer withdrew, 3 did not submit; D and E left CST talks</t>
+          <t>4 whole-company bidders asked to update; 1 NDA signer withdrew; D, E withdrew; J and 3–9 other signers (most likely 3) did not submit</t>
         </is>
       </c>
     </row>
@@ -4918,12 +5659,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Board asked the four whole-company bidders for higher updated IOIs before choosing the second round</t>
+          <t>Board requires updated, higher IOIs from the four whole-company bidders before selecting the second round</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>4: Party A, Parent (strategic); Party H, Party I (financial). Party J still being received, not admitted. Segment bids of C, G, K held for evaluation. Post-Reuters financial NDA signer invited (date uncertain)</t>
+          <t>4 admitted: Party A, Parent (strategic); Party H, Party I (financial). Still being received, not admitted: Party J (bid 07/19); post-Reuters financial NDA signer (invited, no proposal); Parties C, G, K (proposals held, no revision asked).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -4943,12 +5684,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4 responded: Party A $45.00, Party H $42.00–$45.00, Parent $45.00; Party I held $40.00</t>
+          <t>4: Party A $45, Party H $42–45, Parent $45, Party J $38–41. Party I refused to raise $40.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Three advanced (A, H, Parent); Party I and Party J out</t>
+          <t>three advanced (A, H, Parent); I and J out</t>
         </is>
       </c>
     </row>
@@ -4964,42 +5705,88 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Board advanced Party A, Party H and Parent to a second round with fuller diligence; final bid procedures letter followed</t>
+          <t>Board admits Party A, Party H and Parent to the 'second round' with more diligence material</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3: Party A, Parent (strategic); Party H (financial). Segment bidders kept in view: Party K, Party C (strategic); Party G until 08/04</t>
+          <t>3: Party A, Parent (strategic); Party H (financial). Held segment proposals: Party K, Party C, Party G (G withdrew 08/04).</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>09/08/2021 (markups) → 09/15/2021 (final IOIs)</t>
+          <t>none stated</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Passed without action; Late bids accepted</t>
+          <t>No deadline stated</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>Not final</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>all three sent the final bid procedures letter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>44423</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Final bid procedures letter (sent after 08/11, by 08/20): markups due 09/08, final IOIs due 09/15</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3: Party A, Parent (strategic); Party H (financial). Still being received, not admitted: Party K (updated chemical-segment bid on request, 09/09), Party C (standing CST proposal).</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>09/15/2021 (final IOIs; merger agreement markups separately due 09/08/2021)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Late bids accepted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>Announced as final</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Whole company: 2 — Parent ($46.00, $46.50) and Party A ($40.50, $42.00, $44.00). Other-scope: Party K (chemical segment), Party A (polymer alternative)</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Signing with Parent 09/27/2021; Party H withdrew 08/20; Party A, Party K, Party C not selected</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2: Parent $46.00 then $46.50 (best and final); Party A $40.50 (+ polymer-segment alternative), $42.00 + earnout, $44.00 + earnout (best and final). Other-scope: Party K.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>signing with Parent 09/27/2021; H withdrew 08/20; A, K, C not selected</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
+  <autoFilter ref="A1:J5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5010,14 +5797,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
@@ -5067,27 +5854,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Is this one sale process, with round 1 opened 05/24/2021, round 2 at the 07/06 request for improved IOIs, and round 3 at the 07/20 second-round invitation that includes the final bid letter?</t>
+          <t>Process and round map: is this one process with four rounds (R1 outreach 05/24; R2 updated-IOI request 07/06; R3 second-round admission 07/20; R4 final bid letter), with the 2020–21 CST divestiture talks as round 0?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes. One process, three rounds as recorded; no Process restarted row.</t>
+          <t>Yes. Most plausible alternative: merge R3 and R4 into one 'second round' opened 07/20, with the final letter as a Deadline set (moves round-4 rows #50–#73 to round 3). Less plausible: fold the 07/06 request into round 1 (moves #31–#47).</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>C7: (a) fails, so no break: on 05/20 the board carried the CST parties C, D, E, G into the whole-company sale (p.33). Gap of two months or more: undated end of the 'late 2020 and early 2021' CST talks (uncertain) to the 05/24/2021 outreach (p.34), with no other contact gap. (b) is uncertain. (c) is met by the fresh start on 05/20. On 07/06 the board picked four bidders and asked for more value (p.35); on 07/20 it admitted three to diligence (p.36).</t>
+          <t>E6 counts each selection-and-new-request (07/06, p. 35), each information stage (07/20, p. 36), and the first final-bid request (p. 37) as separate rounds. Gap of about two months or more: CST talks 'late 2020 and early 2021' to end-May 2021 outreach, undated. E5: (a) fails, CST parties still in view (p. 33); (b) not established; (c) met on 05/20. One process.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#2, #3, #4, #6, #7, #26, #33, #37</t>
+          <t>#2, #9, #10, #11, #31, #45, #50</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Main alternative boundary: round 4 opens at the final bid letter (#37), moving #44–#59 into it. Second alternative: fold round 2 into round 1, with 07/19 a revised deadline (#29–#32). Starting the process on 05/20 would demote #2–#4 to background.</t>
+          <t>Round counts and finality: merged R3/R4 gives three rounds with the second 'Announced as final'. Merging R2 into R1 treats the 07/19 IOIs as price bargaining rather than a new solicitation.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -5100,27 +5887,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Did the CST-only parties C, D, E and G enter the process (admitted by the June CST management meetings), so that they get exits?</t>
+          <t>Are the named first-round respondents (Party A, Parent, Party J, Party K; Party H, Party I) members of the 10 NDA signers?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Yes. Record entry at #10, their exits, and C not selected at signing; keep them out of whole-company live counts in analysis.</t>
+          <t>Treat them as members, as the ledger does: exactly 1 strategic and 2 financial signers did not submit. Counts are left as ranges (1–5, 2–4) because membership is not stated.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Management held CST-specific preliminary meetings with all four (p.34), and the board said their proposals would be weighed with whole-company bids (p.33). C and G then bid for CST portions (p.35). No NDA with them is reported.</t>
+          <t>The process letter went to each NDA signer and the IOIs came 'as part of the first-round process' (pp. 34–35). The filing never says the named bidders signed NDAs.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#3, #10, #13, #14, #17, #18, #36, #61</t>
+          <t>#13, #14, #25, #26, #27, #28</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If they never entered, #17, #18, #36 and #61 are dropped and #10 becomes an information note. Whole-company counts are unchanged.</t>
+          <t>If some named bidders were not signers, they enter on their bid rows, first-round live units rise by up to six, and more signers did not submit.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -5133,27 +5920,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Are Party A, Parent, Party J, Party K (strategic) and Party H, Party I (financial) among the 10 NDA signers reported by late June?</t>
+          <t>Should segment-only parties (Parties C, D, E, G on CST; Party K on the chemical segment) count as live bidder units?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Yes. Treat them as members; they get no separate NDA rows, and the residual non-submitters are 3.</t>
+          <t>Keep them as participants with their own entries and exits, as recorded, but exclude them from whole-company competition in estimation. They can be identified by Other-scope bid rows and the CST/segment Notes.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The process letter went to NDA signers, and the four IOIs came 'as part of the first-round process' (p.34–35). A strategic/financial split of 6/4 with five strategic and four financial management meetings fits A, Parent, J, K, the inbound party and one strategic withdrawal. No party is named as a signer.</t>
+          <t>The Board said it would weigh CST proposals against whole-company bids (p. 33) and kept C, G and K proposals in view (p. 35). None bid for the whole company.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#9, #11, #12, #25</t>
+          <t>#15, #18, #19, #26, #29, #30, #32, #48, #56, #71, #72</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>If J or K did not sign, the residual in #25 rises to 4 or 5, and J/K enter at their bids. The auction screen stays Met (at least 10 NDA parties).</t>
+          <t>Excluding them drops C, D, E, G and K rows from live counts; whole-company live units at R2 opening fall from 7 to 4.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -5166,27 +5953,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Several proposals are not per-share, whole-company bids (CST portions in $ totals, chemical segment at EBITDA multiples, polymer segment at EV). Should any be converted to per-share values?</t>
+          <t>Deadline outcomes: R1 06/29 Enforced; R2 07/19 Enforced; R3 no due date; R4 09/15 Late bids accepted. Are these right?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>No. Keep them as Other-scope bids with blank price cells and terms in the Note.</t>
+          <t>Yes. For R1, 'Late bids accepted' is possible if any IOI came 06/30–07/02, but the filing does not show it. The 09/08 markup date is treated as a document deadline, not a bid due date.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>C1/C15 forbid constructing whole-company prices. The filing gives no per-share figure for these; the board valued them only through Sum of the Parts ranges (~$44–$51 on 08/22, ~$46–$48 on 09/18; p.37, 39).</t>
+          <t>R1 bids arrived 'By July 2' and the Board acted 07/06 without waiting for Party J (p. 35). R2 responses came 'By July 19' and the Board selected 07/20 (p. 36). Party A bid 09/17, after the 09/15 due date, and the Board reviewed it 09/18 (p. 39).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#13, #14, #23, #45, #49</t>
+          <t>#20, #38, #57, #59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>None for whole-company bid prices. If the board's SOTP ranges were read as bids, K and A would gain priced rows, which is not supported.</t>
+          <t>If the 09/08 markup date counts as a bid deadline, R4 gets a second outcome (Enforced; both markups on time) and a Deadline row.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -5199,27 +5986,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Deadline outcomes: R1 06/29 Late bids accepted; R2 07/19 Enforced; R3 09/08 Passed without action; R3 09/15 Late bids accepted. Correct?</t>
+          <t>Party J missed the 06/29 due date, announced a mid-July bid, and bid $38–$41 on 07/19 without being asked. Is 'Did not submit', then 'Re-entered', right?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Yes, as recorded in Rounds.</t>
+          <t>Yes. The alternative keeps J live throughout as a late round-1 bidder, with no exit or re-entry; either way J is out at the 07/20 selection.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>R1: Party J, which got the letter as an assumed signer, bid on 07/19 and the board weighed it on 07/20 (p.36). R2: the board chose three bidders on 07/20 from bids in hand (p.36). R3: markups arrived on 09/08 and bidding simply went on (p.38). Party A bid on 09/17, after the 09/15 date, and was considered on 09/18 (p.39).</t>
+          <t>J was not among the four asked for updated IOIs on 07/06 (p. 35); its 07/19 IOI was received (p. 36).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#15, #24, #25, #26, #28, #32, #37, #44, #47, #48</t>
+          <t>#25, #43, #44, #47</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>If J's IOI is counted as round 2, R1 becomes Enforced and #28 moves to round 2. If the 09/08 markup date is not a bid due date, R3 has one date only.</t>
+          <t>Under the alternative, J is live at the R2 opening and its 07/19 bid is round 1, a late bid.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -5232,27 +6019,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>When did the six post-Reuters inbound parties approach, and which round does the financial NDA signer belong to?</t>
+          <t>Post-Reuters financial NDA signer: what exit label and date?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Keep the window 07/06–09/27 sorted at its midpoint (08/16) and assign them to round 2.</t>
+          <t>'Did not submit' by signing (09/27), round 2, as recorded. If its NDA preceded 07/20, 'Dropped by target' on 07/20 is equally defensible.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>The filing dates these steps only as after the 07/06 Reuters report (p.35). The financial party got a 'preliminary' management meeting, which suggests a first-round-style invitation, and it never bid (p.35–36).</t>
+          <t>It signed an NDA and met management after 07/06 but 'did not submit any proposal' (pp. 35–36). Its dates are not given.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#39, #40, #41, #62</t>
+          <t>#36, #37, #73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>An earlier sort (July) moves #39–#41 ahead of #33. The live count in round 2 rises by one for that party; round 3 is unchanged if it was never admitted.</t>
+          <t>A 07/20 drop would remove it from live units in rounds 3–4 (live units at R4 opening 6 → 5).</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -5265,27 +6052,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Should Parent's 09/15 and 09/20 bids carry Light conditions although its debt commitment letter was still in draft?</t>
+          <t>Party I's inferred 07/20 drop: should the exit reason be 'Would not improve earlier offer' or 'Not stated'?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Yes, Light.</t>
+          <t>'Would not improve earlier offer'. Party I was asked for greater value and refused to raise $40.00.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Parent said it had completed substantially all diligence (p.39), and its 09/08 markup made financing no condition to closing (p.38). A draft debt commitment letter was circulating on 09/20 (p.39), but the filing never reports financing as uncommitted, and C14 needs a reported absence for Heavy.</t>
+          <t>E14 gives this reason to a bidder asked to improve that declines, even where the target then chooses rivals. The refusal is reported (p. 36).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#46, #51</t>
+          <t>#42, #46</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>If Heavy on financing, the winner's formal bids become heavily conditional, which affects priority-3 reinterpretation.</t>
+          <t>'Not stated' would lose the valuation signal (I's value is about $40).</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -5298,33 +6085,66 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Is Party A's 09/17 $40.50 bid Formal with Heavy conditions?</t>
+          <t>Should the 09/08 merger agreement markups be Bid rows carrying the 07/19 price, rather than Other material events?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Yes: Formal, Heavy. Its polymer-segment alternative stays Informal.</t>
+          <t>No. Record them as events and make the next priced offers (09/15 Parent, 09/17 Party A) the first Formal bids.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>A submitted a merger-agreement markup on 09/08 as the final bid letter required (p.37–38), and the 09/17 bid answers that final solicitation, though late. It was 'subject to additional due diligence' (p.39); by 09/24 this had become 'confirmatory' (p.40), which suggests more than confirmatory diligence on 09/17.</t>
+          <t>Neither markup came with a price (p. 38). E11 needs a markup with a priced proposal or in support of one; the prices followed a week later.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>#48, #49, #54</t>
+          <t>#54, #55, #58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>If Informal, A has no Formal bid until #54. Conditions Unclear instead of Heavy would weaken the heavy-conditional flag on #48/#49.</t>
+          <t>As Bid rows, Parent's and Party A's $45.00 would become Formal from 09/08, a week earlier.</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Conditions on Party A's 09/17 and 09/21 bids: Heavy and Unclear?</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Yes. 09/17 'subject to additional due diligence' is Heavy (open-ended, unlike the later 'confirmatory'). 09/21 states no condition while diligence remained open: Unclear.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>On 09/24 Party A described its diligence as confirmatory (p. 40). The 09/17 wording is broader (p. 39). The Board cited 'risks and contingencies' on 09/23 (p. 40).</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>#59, #65</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Light on 09/17 would make Party A's first final-round bid a low-conditionality bid at $40.50.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5338,8 +6158,8 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5362,7 +6182,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Kraton Corporation (NYSE: KRA), Houston, Texas</t>
+          <t>Kraton Corporation (NYSE: KRA), Houston, Texas; specialty polymers and pine-based chemicals</t>
         </is>
       </c>
     </row>
@@ -5374,7 +6194,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>DL Chemical Co., Ltd. (“Parent”), Seoul, a subsidiary of DL Holdings Co., Ltd. (formerly Daelim Industrial), acting through DLC US Holdings, Inc. and DLC US, Inc. (Merger Subsidiary)</t>
+          <t>DL Chemical Co., Ltd. (Parent), a DL Holdings Co., Ltd. subsidiary, through DLC US Holdings, Inc. and DLC US, Inc.</t>
         </is>
       </c>
     </row>
@@ -5386,7 +6206,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic: petrochemical operating company (p.29); debt financing from Goldman Sachs Bank USA plus Parent cash</t>
+          <t>Strategic (South Korean petrochemical operating company)</t>
         </is>
       </c>
     </row>
@@ -5398,7 +6218,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$46.50 per share in cash</t>
+          <t>$46.50 per share in cash; funded with up to $1.75 billion committed debt from Goldman Sachs Bank USA and Parent cash; no financing condition; $63 million termination and reverse termination fees</t>
         </is>
       </c>
     </row>
@@ -5410,7 +6230,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/27/2021 (morning, before market open)</t>
+          <t>09/27/2021</t>
         </is>
       </c>
     </row>
@@ -5422,7 +6242,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/27/2021 (press releases by Kraton and Parent)</t>
+          <t>09/27/2021 (press releases before the NYSE open)</t>
         </is>
       </c>
     </row>
@@ -5434,7 +6254,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DEFM14A, 11/04/2021</t>
+          <t>DEFM14A definitive proxy statement, dated 11/04/2021</t>
         </is>
       </c>
     </row>
@@ -5482,7 +6302,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>None reported. Background only: Kraton sold its Cariflex business to Daelim Industrial (now in Parent's group) for $530 million in March 2020 (p.29). Party A and Party B declined 2020–21 talks about Kraton acquiring or combining with their polymer businesses (Note of #2).</t>
+          <t>None reported. Before the 05/20/2021 sale decision, Kraton's 12/2020 corporate development plan sought polymer acquisitions (Parties A and B declined; no rows) and a CST divestiture (Parties C–G; recorded as round 0).</t>
         </is>
       </c>
     </row>
@@ -5494,7 +6314,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 11 parties — 10 by late June 2021 (6 strategic, 4 financial) plus 1 financial after 07/06/2021. The filing's totals count parties. No post-signing additions (pre-signing subtotal = 11).</t>
+          <t>Met (process 1): 11 parties (10 by late June 2021, 6 strategic and 4 financial, plus 1 post-Reuters financial party)</t>
         </is>
       </c>
     </row>
@@ -5506,7 +6326,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Yes (also segment/asset bids: Party K chemical segment, Party C and Party G CST portions, Party A polymer-segment alternative)</t>
+          <t>Yes. Also other-scope bids: Party K (chemical segment), Parties C and G (portions of the CST business), Party A's alternative (polymer segment with chemical spin-off)</t>
         </is>
       </c>
     </row>
@@ -5518,7 +6338,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars per share for whole-company bids. Other-scope bids are in total dollars, EBITDA multiples or enterprise value, with no per-share figure (Q4).</t>
+          <t>US dollars per share for whole-company bids. Segment bids are stated as totals, EBITDA multiples or enterprise values (see Notes). Party A bids of 09/21 and 09/24 add an unquantified earnout.</t>
         </is>
       </c>
     </row>
@@ -5530,7 +6350,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>J.P. Morgan Securities LLC (sole)</t>
+          <t>J.P. Morgan Securities LLC</t>
         </is>
       </c>
     </row>
@@ -5554,7 +6374,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>After a 2020 strategy review, Kraton's board pursued a plan that included selling its CST business, but made little progress and on 05/20/2021 decided to explore a sale of the whole company. J.P. Morgan contacted 14 listed buyers and one inbound party. Ten signed NDAs, and by 07/02 four whole-company IOIs of $40.00–$45.00 had arrived, plus segment and CST proposals. The board asked for higher bids, then advanced Party A, Party H and DL Chemical (Parent) to a final round with markups due 09/08 and final bids due 09/15. Party H withdrew, and Parent bid $46.00, then $46.50 best and final at the board's request, while Party A offered at most $44.00 plus an earnout. The board rejected sum-of-the-parts alternatives built on Party K's chemical-segment bid and signed with Parent at $46.50 cash on 09/27/2021.</t>
+          <t>After a 2020 strategy review, Kraton sought polymer acquisitions and a sale of its CST business; the effort stalled, and on 05/20/2021 the Board decided to explore a sale of the whole company. J.P. Morgan contacted 14 listed buyers plus one inbound party, and 10 signed NDAs. Four whole-company IOIs ($40–$45) arrived by early July, alongside segment bids from Parties K, C and G. After a round of updated IOIs, Party A, Party H and Parent were taken to a final round; Party H withdrew on 08/20, unable to hold its range. Parent bid $46.00 on 09/15 and, when asked, raised to $46.50 best and final; Party A's lower bids ($40.50, then $42.00 and $44.00 with earnouts) were rejected. Kraton and Parent signed on 09/27/2021 at $46.50 in cash.</t>
         </is>
       </c>
     </row>

--- a/extraction/kraton.xlsx
+++ b/extraction/kraton.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="MM/DD/YYYY"/>
   </numFmts>
   <fonts count="2">
@@ -439,21 +439,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V75"/>
+  <dimension ref="A1:V74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
@@ -461,9 +461,9 @@
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -589,7 +589,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>J.P. Morgan (target)</t>
+          <t>J.P. Morgan</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -614,7 +614,7 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Kraton's financial adviser; attended the Board's September, November and December 2020 strategy meetings and executed the corporate development plan. Board formally approved its engagement 08/11/2021; engagement letter dated 08/13/2021 (p. 6).</t>
+          <t>Kraton's financial adviser; attended the September, November and December 2020 strategy meetings. Board formally approved its engagement for the sale on 08/11/2021; engagement letter dated 08/13/2021 (p. 6); fee about $32 million, mostly contingent on completion (p. 52).</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Kraton (target)</t>
+          <t>Kraton</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -670,7 +670,7 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Board authorizes a corporate development plan: acquire or combine with other parties' polymer businesses and/or sell the crude sulfate turpentine (CST) business, part of the chemical segment. Not a whole-company sale. Ref: $26.25 close 12/14/2020.</t>
+          <t>Board authorizes a corporate development plan: grow the polymer business by acquiring or combining with other parties' polymer businesses (Kraton as buyer; talks with Parties A and B, who declined) and/or sell the CST business, part of the chemical segment. Not a whole-company sale. Ref: $26.25 close 12/14/2020.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -678,11 +678,7 @@
           <t>“On December 14, 2020, the date on which the Board authorized Kraton to pursue the corporate development plan” (p. 32)</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
       <c r="T3" s="3" t="n">
         <v>44179</v>
@@ -700,12 +696,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>late 2020 – early 2021</t>
+          <t>late 2020 and early 2021</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Parties C, D, E and G</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -730,13 +726,13 @@
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated: Kraton management and J.P. Morgan discussed a sale of the CST business (segment only) under the corporate development plan. Party C said it might be interested, subject to further diligence and analysis. Window: after 12/14/2020 authorization, before 05/20/2021 Board review.</t>
+          <t>Target-initiated: management and J.P. Morgan discussed a sale of the CST business (segment only) with each; each said it might be interested, subject to further diligence and analysis. Window runs from the 12/14/2020 authorization to the 05/20/2021 Board review.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -744,7 +740,11 @@
           <t>“Each of Party C, Party D, Party E, and Party G informed Kraton that they might be interested in acquiring Kraton’s CST business, subject to further diligence and analysis.” (p. 32)</t>
         </is>
       </c>
-      <c r="R4" s="2" t="n"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S4" s="2" t="n"/>
       <c r="T4" s="3" t="n">
         <v>44257</v>
@@ -762,12 +762,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>late 2020 – early 2021</t>
+          <t>late 2020 and early 2021</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party F</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -798,15 +798,19 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated: Kraton management and J.P. Morgan discussed a sale of the CST business (segment only) under the corporate development plan. Party D said it might be interested, subject to further diligence and analysis. Window: after 12/14/2020 authorization, before 05/20/2021 Board review.</t>
+          <t>Target-initiated discussion of a sale of the CST business; Party F said it was not interested. Never entered.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>“Each of Party C, Party D, Party E, and Party G informed Kraton that they might be interested in acquiring Kraton’s CST business, subject to further diligence and analysis.” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="n"/>
+          <t>“Party F informed Kraton that it was not interested in acquiring Kraton’s CST business.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S5" s="2" t="n"/>
       <c r="T5" s="3" t="n">
         <v>44257</v>
@@ -824,22 +828,18 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>late 2020 – early 2021</t>
+          <t>05/20/2021</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>King &amp; Spalding LLP</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -853,28 +853,26 @@
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated: Kraton management and J.P. Morgan discussed a sale of the CST business (segment only) under the corporate development plan. Party E said it might be interested, subject to further diligence and analysis. Window: after 12/14/2020 authorization, before 05/20/2021 Board review.</t>
+          <t>Kraton's legal adviser; first shown acting at the 05/20/2021 Board meeting; later reviewed fiduciary duties and drafted and negotiated the merger agreement.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>“Each of Party C, Party D, Party E, and Party G informed Kraton that they might be interested in acquiring Kraton’s CST business, subject to further diligence and analysis.” (p. 32)</t>
+          <t>“Representatives of J.P. Morgan and King &amp; Spalding LLP, Kraton’s legal advisor, also participated in the meeting.” (p. 32)</t>
         </is>
       </c>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="3" t="n">
-        <v>44257</v>
+        <v>44336</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>44179</v>
+        <v>44336</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>44336</v>
@@ -886,22 +884,18 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>late 2020 – early 2021</t>
+          <t>05/20/2021</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Party G</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kraton</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -915,28 +909,26 @@
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated: Kraton management and J.P. Morgan discussed a sale of the CST business (segment only) under the corporate development plan. Party G said it might be interested, subject to further diligence and analysis. Window: after 12/14/2020 authorization, before 05/20/2021 Board review.</t>
+          <t>Board decides to explore a potential sale of all of Kraton after the corporate development plan gained no momentum; directs management and J.P. Morgan to prepare a buyer list, timeline and process for review the following week. Ref: $33.82 close 05/20/2021.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>“Each of Party C, Party D, Party E, and Party G informed Kraton that they might be interested in acquiring Kraton’s CST business, subject to further diligence and analysis.” (p. 32)</t>
+          <t>“the Board determined that it would be in the best interests of Kraton and its stockholders to explore the potential sale of all of Kraton” (p. 33)</t>
         </is>
       </c>
       <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
       <c r="T7" s="3" t="n">
-        <v>44257</v>
+        <v>44336</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>44179</v>
+        <v>44336</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>44336</v>
@@ -948,12 +940,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>late 2020 – early 2021</t>
+          <t>05/20/2021</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Party F</t>
+          <t>Parties C, D, E and G</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -963,7 +955,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -978,27 +970,31 @@
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated discussion of a sale of the CST business (segment only). Party F declined: not interested. Never entered. Window: after 12/14/2020 authorization, before 05/20/2021 Board review.</t>
+          <t>Admission decision: Board will review the CST proposals of C, D, E and G alongside any whole-company proposals, keeping them in the process as segment-only participants (treated as their entry). J.P. Morgan expected clarity on their interest by mid-June; management met each in June.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“Party F informed Kraton that it was not interested in acquiring Kraton’s CST business.” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="n"/>
+          <t>“The Board also informed Kraton’s senior management and J.P. Morgan that it would review any proposals submitted by Party C, Party D, Party E, and Party G” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="3" t="n">
-        <v>44257</v>
+        <v>44336</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>44179</v>
+        <v>44336</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>44336</v>
@@ -1010,25 +1006,25 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>05/20/2021</t>
+          <t>05/24/2021</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>King &amp; Spalding LLP (target)</t>
+          <t>Kraton</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
@@ -1040,24 +1036,28 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Kraton's legal adviser; first shown acting at the 05/20/2021 Board meeting; advised on fiduciary duties and the merger agreement through signing.</t>
+          <t>Board reviews a buyer list (strategic, financial and sponsors with chemical/polymer portfolio companies, including Party A, Party B's parent and Parent), a two-phase process with initial indications on mainly public information in the third week of June, and directs outreach to 14. Ref: $34.33 close.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“Representatives of J.P. Morgan and King &amp; Spalding LLP, Kraton’s legal advisor, also participated in the meeting.” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n"/>
+          <t>“the Board directed Kraton’s senior management to work with J.P. Morgan to contact the 14 possible acquirers that were discussed at the meeting” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>44336</v>
+        <v>44340</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>44336</v>
+        <v>44340</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>44336</v>
+        <v>44340</v>
       </c>
     </row>
     <row r="10">
@@ -1066,42 +1066,60 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>05/20/2021</t>
+          <t>by 07/02/2021</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Kraton (target)</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Corporate development plan had gained no momentum; Board decides to explore a sale of all of Kraton, orders a buyer list and timeline for review the next week, and will weigh any CST proposals (Parties C, D, E, G) against whole-company proposals. Ref: $33.82 close 05/20/2021.</t>
+          <t>Unclear: no conditions reported. Proposes to buy a portion of the CST business for $100 million (total, not per share). First proposal after the 05/20 Board review, which reported only interest.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>“the Board determined that it would be in the best interests of Kraton and its stockholders to explore the potential sale of all of Kraton” (p. 33)</t>
+          <t>“Party C proposed acquiring a portion of Kraton’s CST business for $100 million” (p. 35)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -1111,13 +1129,13 @@
       </c>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="3" t="n">
-        <v>44336</v>
+        <v>44357</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>44336</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>44336</v>
+        <v>44379</v>
       </c>
     </row>
     <row r="11">
@@ -1126,18 +1144,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>05/24/2021</t>
+          <t>by 07/02/2021</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Kraton (target)</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
+          <t>Party G</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1148,20 +1170,34 @@
       </c>
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Board reviews list of strategic, financial and sponsor-with-portfolio-company buyers (incl. Party A, Party B's parent, Parent); plans two-phase process: IOIs on public information in third week of June, highest-value bidders to a second round. Outreach began end of May. Ref: $34.33 close 05/24/2021.</t>
+          <t>Unclear: price subject to unspecified adjustments; no other condition reported. Proposes to buy a portion of the CST business for $330 million (total, not per share).</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“the Board directed Kraton’s senior management to work with J.P. Morgan to contact the 14 possible acquirers that were discussed at the meeting to explore their interest” (p. 33)</t>
+          <t>“Party G proposed acquiring a portion of Kraton’s CST business for $330 million, subject to adjustments” (p. 35)</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1171,13 +1207,13 @@
       </c>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="3" t="n">
-        <v>44340</v>
+        <v>44357</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>44340</v>
+        <v>44336</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>44340</v>
+        <v>44379</v>
       </c>
     </row>
     <row r="12">
@@ -1191,12 +1227,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14 listed possible acquirers</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1216,13 +1252,13 @@
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated outreach by management/J.P. Morgan; includes Party A, Party B's parent and Parent. Told whole-company bids preferred but stock deals or segment sales would be considered. Five contacted parties declined NDAs; exact arithmetic: 14 − 5 = 9 signed.</t>
+          <t>Target-initiated outreach; Party A was on the 14-party list (p. 33). Earlier (late 2020–early 2021) Party A had declined Kraton's approach to buy its polymer business (p. 32). Parties were told a whole-company bid was preferred but any value-maximizing proposal, including stock or segment deals, would be considered.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1230,11 +1266,7 @@
           <t>“contacted each of the 14 parties discussed with the Board at its May 24, 2021 meeting to explore the parties’ respective interest in a potential acquisition of Kraton” (p. 34)</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="3" t="n">
         <v>44358</v>
@@ -1257,7 +1289,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Unnamed strategic inbound party</t>
+          <t>Parent (DL Chemical Co., Ltd.)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1267,7 +1299,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -1288,12 +1320,12 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Inbound inquiry to J.P. Morgan by a strategic party not on the Board's list; it later signed an NDA (counted in the six strategic signers, next row).</t>
+          <t>Target-initiated outreach; Parent was on the 14-party list (p. 33). Parent, a Korean petrochemical company owned by DL Holdings, bought Kraton's Cariflex business for $530 million in March 2020 (p. 29).</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>“a potential strategic acquirer that was not included on the list of possible acquirers made an “inbound” inquiry and contacted representatives of J.P. Morgan regarding a potential acquisition of Kraton” (p. 34)</t>
+          <t>“contacted each of the 14 parties discussed with the Board at its May 24, 2021 meeting to explore the parties’ respective interest in a potential acquisition of Kraton” (p. 34)</t>
         </is>
       </c>
       <c r="R13" s="2" t="n"/>
@@ -1314,22 +1346,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>by late June 2021</t>
+          <t>end of May and June 2021</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6 strategic NDA signers</t>
+          <t>Party B's parent company</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1344,23 +1376,23 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Stated total 10 NDAs: 6 strategic (incl. inbound party), 4 financial; standstills lapse on an announced definitive agreement. June preliminary management meetings (near-term performance, innovation projects) for 9 signers (5 strategic, 4 financial). Party A, Parent, Party J, Party K presumed members, not stated.</t>
+          <t>Target-initiated outreach; on the 14-party list (p. 33). Party B (strategic) had declined a polymer combination earlier. Whether its parent signed a confidentiality agreement or was among the five decliners is not reported.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>“By late June 2021, Kraton had entered into confidentiality agreements with 10 parties (including the party that made the “inbound” inquiry), six of which parties were potential strategic acquirers” (p. 34)</t>
+          <t>“contacted each of the 14 parties discussed with the Board at its May 24, 2021 meeting to explore the parties’ respective interest in a potential acquisition of Kraton” (p. 34)</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
@@ -1380,22 +1412,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>by late June 2021</t>
+          <t>end of May and June 2021</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4 financial NDA signers</t>
+          <t>11 other listed parties</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1410,23 +1442,23 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Part of the stated 10 NDAs (6 strategic, 4 financial), standstills included; all four attended June preliminary management meetings. Party H and Party I presumed members, not stated.</t>
+          <t>Count: 11 = 14 listed − Party A, Parent, Party B's parent. Mix of strategic and financial, split not given. With the inbound party, 15 contacted = 10 confidentiality signers + 5 decliners (p. 34); Parties H, I and probably J, K are among these 11.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>“six of which parties were potential strategic acquirers and four of which were potential financial acquirers” (p. 34)</t>
+          <t>“contacted each of the 14 parties discussed with the Board at its May 24, 2021 meeting to explore the parties’ respective interest in a potential acquisition of Kraton” (p. 34)</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S15" s="2" t="n"/>
@@ -1446,12 +1478,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>June 2021</t>
+          <t>end of May and June 2021</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Parties C, D, E and G</t>
+          <t>Unnamed inbound strategic party</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1461,7 +1493,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1476,18 +1508,18 @@
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Kraton admits the four CST-interested parties to preliminary management meetings on a CST-only sale; treated as their entry (segment scope, not whole company). Window ends 06/17/2021 because Party E withdrew 06/18/2021.</t>
+          <t>Inbound inquiry to J.P. Morgan about acquiring Kraton, no price; not on the 14-party list. Signed a confidentiality agreement by late June (inside the strategic cohort); it is not Party A or Parent (both on the list) and may be Party J, Party K or an unnamed signer.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“Kraton’s senior management also participated in preliminary management meetings with Party C, Party D, Party E, and Party G regarding the potential sale of Kraton’s CST business.” (p. 34)</t>
+          <t>“a potential strategic acquirer that was not included on the list of possible acquirers made an “inbound” inquiry and contacted representatives of J.P. Morgan” (p. 34)</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -1500,10 +1532,10 @@
         <v>44358</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>44348</v>
+        <v>44336</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>44364</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="17">
@@ -1512,18 +1544,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>June 2021</t>
+          <t>by late June 2021</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Kraton (target)</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n"/>
+          <t>6 strategic confidentiality signers</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1537,29 +1573,35 @@
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
+      <c r="M17" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>J.P. Morgan's process letter to every NDA signer asks for initial indications of interest by 06/29/2021; bars discussion of management's post-closing roles. Sent before the due date.</t>
+          <t>Count: 6 of 10 signers (p. 34), including the inbound party; by the contact accounting (15 contacted = 10 signers + 5 decliners) Party A, Parent, Party J and Party K are members. Standstills lapse on announcement of a definitive agreement. June preliminary management meetings with 5 strategic signers.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“circulated a process letter to each party that executed a confidentiality agreement that requested initial indications of interest be submitted by June 29, 2021” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="n"/>
+          <t>“Kraton had entered into confidentiality agreements with 10 parties (including the party that made the “inbound” inquiry), six of which parties were potential strategic acquirers” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="n">
-        <v>44361</v>
+        <v>44358</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>44348</v>
+        <v>44336</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>44375</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="18">
@@ -1568,22 +1610,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>June 2021</t>
+          <t>by late June 2021</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Unnamed strategic NDA signer</t>
+          <t>4 financial confidentiality signers</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -1598,31 +1640,31 @@
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Declined the preliminary management meeting and said it was no longer interested. Type by exact arithmetic: 6 strategic signers − 5 strategic attendees = 1; all 4 financial attended.</t>
+          <t>Count: 4 of 10 signers (p. 34); Party H and Party I are members by the contact accounting. All four held June preliminary management meetings reviewing near-term performance and innovation projects, as did five strategic signers.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“declined to participate in, this preliminary management meeting and informed representatives of J.P. Morgan that it was no longer interested in pursuing a potential transaction” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="n"/>
+          <t>“six of which parties were potential strategic acquirers and four of which were potential financial acquirers” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="3" t="n">
-        <v>44362</v>
+        <v>44358</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>44348</v>
+        <v>44340</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>44377</v>
@@ -1634,22 +1676,18 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/18/2021</t>
+          <t>June 2021</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kraton</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -1663,39 +1701,33 @@
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>CST-only participant: no longer interested in acquiring the CST business. Never bid.</t>
+          <t>J.P. Morgan's process letter to every confidentiality signer asks for initial indications of interest by 06/29/2021 and bars discussions with management about post-closing roles (none occurred before signing).</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“On June 18, 2021, Party E informed Kraton that it was no longer interested in acquiring Kraton’s CST business.” (p. 34)</t>
+          <t>“circulated a process letter to each party that executed a confidentiality agreement that requested initial indications of interest be submitted by June 29, 2021” (p. 34)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>44365</v>
+        <v>44361</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>44365</v>
+        <v>44348</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>44365</v>
+        <v>44375</v>
       </c>
     </row>
     <row r="20">
@@ -1704,12 +1736,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>06/23/2021</t>
+          <t>June 2021</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Unnamed strategic signer (declined meeting)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1744,28 +1776,24 @@
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>CST-only participant: no longer interested in acquiring the CST business. Never bid.</t>
+          <t>Declined its preliminary management meeting and said it was no longer interested. Strategic by arithmetic: 6 strategic signers, 5 strategic met management.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“On June 23, 2021, Party D informed Kraton that it was no longer interested in acquiring Kraton’s CST business.” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“One party that executed a confidentiality agreement with Kraton was invited to, but declined to participate in, this preliminary management meeting” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>44370</v>
+        <v>44362</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>44370</v>
+        <v>44348</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>44370</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="21">
@@ -1774,18 +1802,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>06/29/2021</t>
+          <t>06/18/2021</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Kraton (target)</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n"/>
+          <t>Party E</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -1799,33 +1831,39 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
+      <c r="M21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Due date for first-round indications of interest. Four whole-company IOIs received by 07/02/2021; exact arrival days not stated.</t>
+          <t>Segment-only participant: no longer interested in acquiring the CST business. Never bid.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“requested initial indications of interest be submitted by June 29, 2021” (p. 34)</t>
+          <t>“On June 18, 2021, Party E informed Kraton that it was no longer interested in acquiring Kraton’s CST business.” (p. 34)</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="3" t="n">
-        <v>44376</v>
+        <v>44365</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>44376</v>
+        <v>44365</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>44376</v>
+        <v>44365</v>
       </c>
     </row>
     <row r="22">
@@ -1834,12 +1872,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>by 07/02/2021</t>
+          <t>06/23/2021</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1849,7 +1887,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1858,52 +1896,44 @@
       <c r="G22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>No conditions stated; IOI based primarily on public information, diligence still open. Non-binding first-round indication of interest, $42.00–$45.00 per share. Ref: $31.65 close 07/02/2021.</t>
+          <t>Segment-only participant: no longer interested in acquiring the CST business. Never bid.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $42.00 to $45.00, Party H, a financial acquirer, proposed $41.00 to $43.00, Parent proposed $41.00, and Party I, a financial acquirer, proposed $40.00.” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="n"/>
+          <t>“On June 23, 2021, Party D informed Kraton that it was no longer interested in acquiring Kraton’s CST business.” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="n">
-        <v>44376</v>
+        <v>44370</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>44348</v>
+        <v>44370</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>44379</v>
+        <v>44370</v>
       </c>
     </row>
     <row r="23">
@@ -1912,22 +1942,18 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>by 07/02/2021</t>
+          <t>06/29/2021</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Party H</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Kraton</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1936,52 +1962,38 @@
       <c r="G23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>No conditions stated; IOI based primarily on public information, diligence still open. First-round indication of interest, $41.00–$43.00 per share.</t>
+          <t>Due date for initial indications. Four whole-company indications were in hand by 07/02 (arrival days not given); Party J asked for more time. Board then set a further due date of 07/19 (#31).</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $42.00 to $45.00, Party H, a financial acquirer, proposed $41.00 to $43.00, Parent proposed $41.00, and Party I, a financial acquirer, proposed $40.00.” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="n"/>
+          <t>“requested initial indications of interest be submitted by June 29, 2021” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="3" t="n">
         <v>44376</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>44348</v>
+        <v>44376</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>44379</v>
+        <v>44376</v>
       </c>
     </row>
     <row r="24">
@@ -1995,7 +2007,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2015,10 +2027,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2042,12 +2054,12 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>No conditions stated; IOI based primarily on public information, diligence still open. First-round indication of interest at $41.00 per share. Parent (Korean petrochemical company, DL Holdings subsidiary) bought Kraton's Cariflex business in 2020 (p. 29).</t>
+          <t>Unclear: no stated conditions; first-round indication on mainly public information with diligence continuing. Initial indication of interest, whole company. Ref: $31.65 close 07/02/2021.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $42.00 to $45.00, Party H, a financial acquirer, proposed $41.00 to $43.00, Parent proposed $41.00, and Party I, a financial acquirer, proposed $40.00.” (p. 35)</t>
+          <t>“The per share purchase prices proposed by these parties were as follows: Party A proposed $42.00 to $45.00” (p. 35)</t>
         </is>
       </c>
       <c r="R24" s="2" t="n"/>
@@ -2073,7 +2085,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Party I</t>
+          <t>Party H</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2093,10 +2105,10 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2120,12 +2132,12 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>No conditions stated; IOI based primarily on public information, diligence still open. First-round indication of interest at $40.00 per share.</t>
+          <t>Unclear: no stated conditions; first-round indication on mainly public information with diligence continuing. Initial indication of interest, whole company.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $42.00 to $45.00, Party H, a financial acquirer, proposed $41.00 to $43.00, Parent proposed $41.00, and Party I, a financial acquirer, proposed $40.00.” (p. 35)</t>
+          <t>“Party H, a financial acquirer, proposed $41.00 to $43.00” (p. 35)</t>
         </is>
       </c>
       <c r="R25" s="2" t="n"/>
@@ -2151,7 +2163,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Party J</t>
+          <t>Parent (DL Chemical Co., Ltd.)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2161,7 +2173,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -2170,42 +2182,52 @@
       <c r="G26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
+      <c r="H26" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason</t>
-        </is>
-      </c>
+      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>No IOI by the 06/29/2021 due date; J told J.P. Morgan it intended to bid in mid-July. Treated as a presumed NDA signer eligible for round 1. Re-enters at #43.</t>
+          <t>Unclear: no stated conditions; first-round indication on mainly public information with diligence continuing. Initial indication of interest, whole company.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“Party J, a strategic acquirer, informed representatives of J.P. Morgan that it intended to submit a proposal to acquire Kraton during the middle of July.” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>Q2; Q5</t>
-        </is>
-      </c>
+          <t>“Parent proposed $41.00, and Party I , a financial acquirer, proposed $40.00” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="3" t="n">
         <v>44376</v>
       </c>
-      <c r="U26" s="2" t="n"/>
+      <c r="U26" s="3" t="n">
+        <v>44348</v>
+      </c>
       <c r="V26" s="3" t="n">
-        <v>44376</v>
+        <v>44379</v>
       </c>
     </row>
     <row r="27">
@@ -2219,17 +2241,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Party K</t>
+          <t>Party I</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -2238,8 +2260,12 @@
       <c r="G27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
+      <c r="H27" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>40</v>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -2252,7 +2278,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
@@ -2262,24 +2288,22 @@
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Heavy: J.P. Morgan later reported this proposal subject to significant diligence and firm financing commitments (p. 37); only a standalone deal, no back-to-back polymer sale. Chemical segment at 9.0x–10.0x trailing-12-month (June 2021) segment adjusted EBITDA; no price stated.</t>
+          <t>Unclear: no stated conditions; first-round indication on mainly public information with diligence continuing. Initial indication of interest, whole company.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“Party K, a potential strategic acquirer, proposed acquiring Kraton’s chemical segment.” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>Q2; Q3</t>
-        </is>
-      </c>
+          <t>“Parent proposed $41.00, and Party I , a financial acquirer, proposed $40.00” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="3" t="n">
         <v>44376</v>
       </c>
-      <c r="U27" s="2" t="n"/>
+      <c r="U27" s="3" t="n">
+        <v>44348</v>
+      </c>
       <c r="V27" s="3" t="n">
         <v>44379</v>
       </c>
@@ -2290,12 +2314,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>by 06/29/2021</t>
+          <t>by 07/02/2021</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Remaining strategic NDA signers (unnamed)</t>
+          <t>Party K</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2305,7 +2329,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2316,42 +2340,50 @@
       </c>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Count: 1–5. Six strategic signers − 1 withdrawal (#17) = 5, less Party A, Parent, Party J (own row) and Party K if they were signers (likely, not stated): exactly 1 if all four were. No submission reported.</t>
+          <t>Heavy: J.P. Morgan said on 08/30 this proposal was still subject to significant diligence and firm financing commitments (p. 37). Chemical segment only, at 9.0x–10.0x segment adjusted EBITDA for the 12 months to June 2021; no dollar price; only if independent of any polymer sale.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“By July 2, 2021, Kraton received four indications of interest as part of the first-round process that contemplated a potential acquisition of all of Kraton.” (p. 35)</t>
+          <t>“Party K, a potential strategic acquirer, proposed acquiring Kraton’s chemical segment. Party K did not propose a specific purchase price” (p. 35)</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="3" t="n">
         <v>44376</v>
       </c>
-      <c r="U28" s="2" t="n"/>
+      <c r="U28" s="3" t="n">
+        <v>44348</v>
+      </c>
       <c r="V28" s="3" t="n">
-        <v>44376</v>
+        <v>44379</v>
       </c>
     </row>
     <row r="29">
@@ -2365,12 +2397,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Remaining financial NDA signers (unnamed)</t>
+          <t>1 unnamed strategic signer</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2389,7 +2421,9 @@
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
+      <c r="M29" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -2402,7 +2436,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Count: 2–4. Four financial signers less Party H and Party I if they were signers (likely, not stated): exactly 2 if both were. No submission reported.</t>
+          <t>Count: 6 strategic signers − Party A, Parent, Party J, Party K − 1 withdrawal (#19) = 1; met management, no submission reported in round 1.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -2412,7 +2446,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S29" s="2" t="n"/>
@@ -2430,22 +2464,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>by 07/02/2021</t>
+          <t>by 06/29/2021</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>2 unnamed financial signers</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2456,34 +2490,30 @@
       </c>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Unclear: no condition stated; earlier interest was subject to further diligence. Proposes to buy a portion of the CST business for $100 million (total, not per share).</t>
+          <t>Count: 4 financial signers − Party H, Party I = 2; met management, no submission reported in round 1.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“Party C proposed acquiring a portion of Kraton’s CST business for $100 million” (p. 35)</t>
+          <t>“By July 2, 2021, Kraton received four indications of interest as part of the first-round process that contemplated a potential acquisition of all of Kraton.” (p. 35)</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
@@ -2493,11 +2523,11 @@
       </c>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="3" t="n">
-        <v>44379</v>
+        <v>44376</v>
       </c>
       <c r="U30" s="2" t="n"/>
       <c r="V30" s="3" t="n">
-        <v>44379</v>
+        <v>44376</v>
       </c>
     </row>
     <row r="31">
@@ -2511,7 +2541,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Party G</t>
+          <t>Party J</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2521,7 +2551,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2532,21 +2562,9 @@
       </c>
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n">
         <v>1</v>
       </c>
@@ -2554,17 +2572,17 @@
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Unclear: subject to unspecified adjustments; earlier interest was subject to further diligence. Proposes to buy a portion of the CST business for $330 million (total, not per share).</t>
+          <t>Misses the 06/29 due date: tells J.P. Morgan it intends to submit a whole-company proposal in mid-July. Board noted this on 07/06. Party J received the process letter as a confidentiality signer.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“Party G proposed acquiring a portion of Kraton’s CST business for $330 million, subject to adjustments.” (p. 35)</t>
+          <t>“Party J, a strategic acquirer, informed representatives of J.P. Morgan that it intended to submit a proposal to acquire Kraton during the middle of July.” (p. 35)</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S31" s="2" t="n"/>
@@ -2587,20 +2605,20 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Kraton (target)</t>
+          <t>Kraton</t>
         </is>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
@@ -2612,7 +2630,7 @@
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Board, reviewing the four whole-company IOIs, tells Party A, Party H, Parent and Party I it requires updated IOIs ascribing greater value by 07/19 before choosing any second-round invitees. Filing prints 'July 19, 2020'; context shows 2021.</t>
+          <t>Board requires updated indications from Parties A, H, Parent and I, ascribing greater value, by 07/19 before deciding who enters the second round. Filing prints “July 19, 2020”, evidently 2021.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -2622,7 +2640,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S32" s="2" t="n"/>
@@ -2664,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
@@ -2678,17 +2696,17 @@
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Board decides not to ask Party C, Party G or Party K for revised segment proposals 'at this time'; their proposals kept for evaluation alongside updated whole-company proposals. Not an exit.</t>
+          <t>Board decides not to ask the segment bidders for revised proposals for now; their proposals to be evaluated against the updated whole-company proposals.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“The Board also determined not to request that Party C, Party G, or Party K submit revised indications of interest regarding their proposals to acquire portions of” (p. 35)</t>
+          <t>“The Board also determined not to request that Party C , Party G , or Party K submit revised indications of interest” (p. 35)</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S33" s="2" t="n"/>
@@ -2726,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
@@ -2738,12 +2756,12 @@
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Media report that Kraton hired J.P. Morgan for a potential sale. Ref: $31.65 close 07/02/2021 (last unaffected day); $36.37 close 07/06/2021; $34.51–$42.80 closes thereafter to signing.</t>
+          <t>Media report: Reuters says Kraton hired J.P. Morgan to advise on a potential sale. Ref: $36.37 close 07/06/2021; closes ranged $34.51–$42.80 from then to signing.</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“Reuters published a report stating, among other matters, that Kraton had hired J.P. Morgan as its financial advisor to advise Kraton with respect to a potential sale of the company” (p. 35)</t>
+          <t>“Also on July 6, 2021, Reuters published a report stating, among other matters, that Kraton had hired J.P. Morgan as its financial advisor” (p. 35)</t>
         </is>
       </c>
       <c r="R34" s="2" t="n"/>
@@ -2786,7 +2804,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
@@ -2800,7 +2818,7 @@
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Inbound inquiries to J.P. Morgan after the Reuters report; invited to sign an NDA and bid; all five declined NDAs and made no proposals, so never entered.</t>
+          <t>Inbound inquiries to J.P. Morgan about the process after the Reuters report; each invited to sign a confidentiality agreement and propose; all five declined to sign and never proposed. Never entered.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -2808,7 +2826,11 @@
           <t>“J.P. Morgan received inbound inquiries from six additional parties, five of which were strategic acquirers, and one of which was a financial acquirer” (p. 35)</t>
         </is>
       </c>
-      <c r="R35" s="2" t="n"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="3" t="n">
         <v>44383</v>
@@ -2829,7 +2851,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Post-Reuters financial party</t>
+          <t>Unnamed financial party (post-Reuters)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2846,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
@@ -2860,15 +2882,19 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Inbound inquiry to J.P. Morgan after the Reuters report; invited to sign an NDA and submit a proposal.</t>
+          <t>Inbound inquiry after the Reuters report; invited to sign a confidentiality agreement and submit a proposal.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“J.P. Morgan received inbound inquiries from six additional parties, five of which were strategic acquirers, and one of which was a financial acquirer” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="n"/>
+          <t>“Each of these parties were invited to execute a confidentiality agreement and submit a proposal to acquire Kraton.” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="3" t="n">
         <v>44383</v>
@@ -2889,7 +2915,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Post-Reuters financial party</t>
+          <t>Unnamed financial party (post-Reuters)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2906,7 +2932,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
@@ -2920,17 +2946,17 @@
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Late entrant signs an NDA (11th confidentiality agreement in the process). Execution date not stated.</t>
+          <t>Eleventh confidentiality signer; also held a preliminary management meeting. Execution date not given beyond “after” 07/06.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“Of these six parties, one party, a financial acquirer, executed a confidentiality agreement with Kraton” (p. 35)</t>
+          <t>“one party, a financial acquirer, executed a confidentiality agreement with Kraton and participated in a preliminary management meeting” (p. 35)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S37" s="2" t="n"/>
@@ -2948,35 +2974,51 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>after 07/06/2021</t>
+          <t>by 07/19/2021</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Post-Reuters financial party</t>
+          <t>Party J</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="n">
         <v>1</v>
       </c>
@@ -2984,27 +3026,29 @@
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Catch-up access: Kraton holds a preliminary management meeting with the late entrant, the access first-round NDA signers had in June. Date not stated.</t>
+          <t>Unclear: no stated conditions; first-round indication. Late whole-company indication (first price from J), received without a new due date for J; J said it would not go above this range.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“executed a confidentiality agreement with Kraton and participated in a preliminary management meeting with Kraton’s senior” (p. 35)</t>
+          <t>“Party J also submitted an indication of interest that proposed an acquisition of Kraton at a per share purchase price of $38.00 to $41.00 per share.” (p. 36)</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="3" t="n">
-        <v>44383</v>
+        <v>44389</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>44383</v>
       </c>
-      <c r="V38" s="2" t="n"/>
+      <c r="V38" s="3" t="n">
+        <v>44396</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3012,55 +3056,73 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/19/2021</t>
+          <t>by 07/19/2021</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Kraton (target)</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n"/>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Due date for updated IOIs from the four whole-company bidders; responses received by 07/19/2021.</t>
+          <t>Unclear: no stated conditions; updated indication with diligence continuing. Revises #23 from $42.00–$45.00 to a point price.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“By July 19, 2021, Kraton received updated indications of interest with respect to a potential acquisition of the entire Company” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>“Party A proposed $45.00, Party H proposed $42.00 to $45.00, and Parent proposed $45.00” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="n"/>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="3" t="n">
         <v>44396</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>44396</v>
+        <v>44383</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>44396</v>
@@ -3077,12 +3139,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Party H</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3094,10 +3156,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>45</v>
@@ -3124,12 +3186,12 @@
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>No conditions stated; second-round diligence not yet opened. Updated IOI at $45.00, up from $42.00–$45.00 (#21).</t>
+          <t>Unclear: no stated conditions; updated indication with diligence continuing. Revises #24 from $41.00–$43.00.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $45.00, Party H proposed $42.00 to $45.00, and Parent proposed $45.00.” (p. 36)</t>
+          <t>“Party A proposed $45.00, Party H proposed $42.00 to $45.00, and Parent proposed $45.00” (p. 36)</t>
         </is>
       </c>
       <c r="R40" s="2" t="n"/>
@@ -3155,12 +3217,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Party H</t>
+          <t>Parent (DL Chemical Co., Ltd.)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3172,10 +3234,10 @@
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I41" s="4" t="n">
         <v>45</v>
@@ -3202,12 +3264,12 @@
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>No conditions stated; second-round diligence not yet opened. Updated IOI at $42.00–$45.00, up from $41.00–$43.00 (#22).</t>
+          <t>Unclear: no stated conditions; updated indication with diligence continuing. Revises #25 from $41.00.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $45.00, Party H proposed $42.00 to $45.00, and Parent proposed $45.00.” (p. 36)</t>
+          <t>“Party A proposed $45.00, Party H proposed $42.00 to $45.00, and Parent proposed $45.00” (p. 36)</t>
         </is>
       </c>
       <c r="R41" s="2" t="n"/>
@@ -3233,46 +3295,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
+          <t>Party I</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n">
         <v>1</v>
       </c>
@@ -3280,15 +3326,19 @@
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>No conditions stated; second-round diligence not yet opened. Updated IOI at $45.00, up from $41.00 (#23).</t>
+          <t>Declines the Board's request for a higher value: will not increase its $40.00 indication (#26). No new bid.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“Party A proposed $45.00, Party H proposed $42.00 to $45.00, and Parent proposed $45.00.” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="n"/>
+          <t>“Party I stated that it was not willing to increase its proposed purchase price of $40.00 per share.” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="3" t="n">
         <v>44396</v>
@@ -3306,53 +3356,47 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>by 07/19/2021</t>
+          <t>07/19/2021</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Party I</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Kraton</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
-      <c r="M43" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M43" s="2" t="n"/>
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Party I answers the request for greater value by refusing to raise its $40.00 (#24); no new bid.</t>
+          <t>Due date for updated indications from A, H, Parent and I; all four responded by it. Board acted on the bids in hand on 07/20.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“Party I stated that it was not willing to increase its proposed purchase price of $40.00 per share.” (p. 36)</t>
+          <t>“By July 19, 2021, Kraton received updated indications of interest with respect to a potential acquisition of the entire Company” (p. 36)</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S43" s="2" t="n"/>
@@ -3360,7 +3404,7 @@
         <v>44396</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>44383</v>
+        <v>44396</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>44396</v>
@@ -3372,29 +3416,29 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>by 07/19/2021</t>
+          <t>07/20/2021</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Party J</t>
+          <t>Party I</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
@@ -3404,30 +3448,40 @@
       <c r="M44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="n"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Would not improve earlier offer</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Party J returns after not submitting in round 1 (#25), with its announced mid-July bid; not among the four asked for updated IOIs, so received but not admitted.</t>
+          <t>Not among the three invited to round 2 (complete set named), after refusing to raise its $40.00 indication when asked (#41).</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“Party J also submitted an indication of interest that proposed an acquisition of Kraton at a per share purchase price of $38.00 to $41.00 per share.” (p. 36)</t>
+          <t>“invite Party A , Party H, and Parent to the second round of the transaction process” (p. 36)</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="3" t="n">
-        <v>44396</v>
-      </c>
-      <c r="U44" s="2" t="n"/>
+        <v>44397</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>44397</v>
+      </c>
       <c r="V44" s="3" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
     </row>
     <row r="45">
@@ -3436,7 +3490,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>by 07/19/2021</t>
+          <t>07/20/2021</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3451,63 +3505,57 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" s="2" t="n"/>
-      <c r="O45" s="2" t="n"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>No conditions stated; diligence open. First IOI, $38.00–$41.00, and J said it would not go above this range. Unsolicited in round 2.</t>
+          <t>Not among the three invited to round 2 (complete set named). J had bid $38.00–$41.00 and said it would not go higher; it was not asked to improve, so no reason is attributed.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“Party J also submitted an indication of interest that proposed an acquisition of Kraton at a per share purchase price of $38.00 to $41.00 per share.” (p. 36)</t>
+          <t>“invite Party A , Party H, and Parent to the second round of the transaction process” (p. 36)</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>44396</v>
-      </c>
-      <c r="U45" s="2" t="n"/>
+        <v>44397</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>44397</v>
+      </c>
       <c r="V45" s="3" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
     </row>
     <row r="46">
@@ -3516,47 +3564,61 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>07/20/2021</t>
+          <t>after 07/06/2021; by 09/27/2021</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Kraton (target)</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n"/>
+          <t>Unnamed financial party (post-Reuters)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
+      <c r="M46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Board selects Party A, Party H and Parent for the filing's 'second round' and gives all three additional financial and diligence materials; diligence management meetings week of 08/09/2021. No bid due date yet. Board also asks for analysis of separate segment sales.</t>
+          <t>Filing reports it never submitted a proposal after being invited to; timing inferred. Sorted at the 07/20 advancement decision, which named a complete set without it.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>“the Board instructed representatives of J.P. Morgan and Kraton’s senior management to invite Party A, Party H, and Parent to the second round of the transaction process” (p. 36)</t>
+          <t>“management but did not submit any proposal with respect to a transaction.” (p. 36)</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S46" s="2" t="n"/>
@@ -3564,10 +3626,10 @@
         <v>44397</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>44397</v>
+        <v>44383</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>44397</v>
+        <v>44466</v>
       </c>
     </row>
     <row r="47">
@@ -3581,17 +3643,13 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Party I</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Kraton</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -3605,32 +3663,22 @@
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>Would not improve earlier offer</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Not in the named advancing set (#45). Party I had been asked for greater value and refused to raise $40.00 (#42).</t>
+          <t>Board advances Parties A and H and Parent, to receive additional financial and diligence materials (alike for all three); diligence management meetings week of 08/09. No bid requested. Board also asks J.P. Morgan to analyse separate segment sales.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>“the Board instructed representatives of J.P. Morgan and Kraton’s senior management to invite Party A, Party H, and Parent to the second round of the transaction process” (p. 36)</t>
+          <t>“the Board instructed representatives of J.P. Morgan and Kraton’s senior management to invite Party A , Party H, and Parent to the second round of the transaction process” (p. 36)</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S47" s="2" t="n"/>
@@ -3650,12 +3698,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>07/20/2021</t>
+          <t>08/04/2021</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Party J</t>
+          <t>Party G</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3665,7 +3713,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -3687,35 +3735,31 @@
           <t>Not stated</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Not in the named advancing set (#45); its $38.00–$41.00 was below the other three bids. J was not asked to improve.</t>
+          <t>Segment-only participant: no longer interested in the CST business; its $330 million proposal (#10) lapses.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>“the Board instructed representatives of J.P. Morgan and Kraton’s senior management to invite Party A, Party H, and Parent to the second round of the transaction process” (p. 36)</t>
+          <t>“On August 4, 2021, Party G informed Kraton that it was no longer interested in acquiring Kraton’s CST business.” (p. 36)</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="3" t="n">
-        <v>44397</v>
+        <v>44412</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>44397</v>
+        <v>44412</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>44397</v>
+        <v>44412</v>
       </c>
     </row>
     <row r="49">
@@ -3724,22 +3768,18 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>08/04/2021</t>
+          <t>after 08/11/2021</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Party G</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kraton</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
@@ -3753,39 +3793,33 @@
       <c r="J49" s="2" t="n"/>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
-      <c r="M49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>CST-only bidder (#30): no longer interested in acquiring the CST business.</t>
+          <t>Final bid procedures letter to Parties A and H and Parent: merger agreement markups due 09/08, final indications due 09/15. Sent after the 08/11 Board meeting authorized the draft merger agreement; sorted at that decision.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>“On August 4, 2021, Party G informed Kraton that it was no longer interested in acquiring Kraton’s CST business.” (p. 36)</t>
+          <t>“J.P. Morgan provided a final bid procedures letter to Party A , Party H, and Parent that requested these bidders to submit markups of a draft merger agreement” (p. 37)</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2; Q7</t>
         </is>
       </c>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="3" t="n">
-        <v>44412</v>
+        <v>44419</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>44412</v>
+        <v>44419</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>44412</v>
+        <v>44446</v>
       </c>
     </row>
     <row r="50">
@@ -3799,7 +3833,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Media outlet 1</t>
+          <t>Media outlet</t>
         </is>
       </c>
       <c r="D50" s="2" t="n"/>
@@ -3824,7 +3858,7 @@
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Media report that potential acquirers had been invited to a second round.</t>
+          <t>Media report that potential acquirers had been invited to a second round (first of two outlets).</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -3850,25 +3884,25 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>after 08/11/2021, by 08/20/2021</t>
+          <t>08/16/2021</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Kraton (target)</t>
+          <t>Media outlet</t>
         </is>
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
@@ -3880,28 +3914,24 @@
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Final bid procedures letter to Party A, Party H and Parent: merger agreement markups due 09/08/2021, final IOIs due 09/15/2021; Board authorized sending the draft merger agreement 08/11. Date to 08/20 inferred: Party H received the letter and quit that day.</t>
+          <t>Second media report that potential acquirers had been invited to a second round.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>“a final bid procedures letter to Party A, Party H, and Parent that requested these bidders to submit markups of a draft merger agreement by September 8, 2021” (p. 37)</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“On August 13 and August 16, 2021, two media outlets each published a report stating, among other matters, that potential acquirers of Kraton had been invited to the second round” (p. 37)</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="n"/>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="3" t="n">
-        <v>44423</v>
+        <v>44424</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>44419</v>
+        <v>44424</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>44428</v>
+        <v>44424</v>
       </c>
     </row>
     <row r="52">
@@ -3910,54 +3940,64 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>08/16/2021</t>
+          <t>08/20/2021</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Media outlet 2</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n"/>
+          <t>Party H</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n"/>
-      <c r="N52" s="2" t="n"/>
+      <c r="M52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Value below earlier offer</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Second media report that potential acquirers had been invited to a second round.</t>
+          <t>Tells Kraton it cannot maintain its $42.00–$45.00 indicative range (#39) and cannot continue in the process.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>“On August 13 and August 16, 2021, two media outlets each published a report stating, among other matters, that potential acquirers of Kraton had been invited to the second round” (p. 37)</t>
+          <t>“On August 20, 2021, Party H informed Kraton that it was unable to maintain its indicative bid price range and was unable to continue in the process.” (p. 37)</t>
         </is>
       </c>
       <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="3" t="n">
-        <v>44424</v>
+        <v>44428</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>44424</v>
+        <v>44428</v>
       </c>
       <c r="V52" s="3" t="n">
-        <v>44424</v>
+        <v>44428</v>
       </c>
     </row>
     <row r="53">
@@ -3966,29 +4006,29 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>08/20/2021</t>
+          <t>08/30/2021</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Party H</t>
+          <t>Party K</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
@@ -3998,32 +4038,32 @@
       <c r="M53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>Value below earlier offer</t>
-        </is>
-      </c>
+      <c r="N53" s="2" t="n"/>
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Party H said it could not maintain its $42.00–$45.00 indicative range (#40) and could not continue, implying value below its earlier offer.</t>
+          <t>Board, finding a sum-of-the-parts sale unlikely to beat a whole-company sale, asks J.P. Morgan to request an updated chemical-segment proposal from K. J.P. Morgan noted K's proposal needed significant diligence and firm financing; Party C's $100 million CST bid was the only other live chemical proposal.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>“Party H informed Kraton that it was unable to maintain its indicative bid price range and was unable to continue in the process.” (p. 37)</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="n"/>
+          <t>“the Board therefore instructed J.P. Morgan to request an updated proposal from Party K regarding its possible acquisition of Kraton’s chemical segment” (p. 38)</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="3" t="n">
-        <v>44428</v>
+        <v>44438</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>44428</v>
+        <v>44438</v>
       </c>
       <c r="V53" s="3" t="n">
-        <v>44428</v>
+        <v>44438</v>
       </c>
     </row>
     <row r="54">
@@ -4032,25 +4072,25 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>08/30/2021</t>
+          <t>09/08/2021</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Kraton (target)</t>
+          <t>Kraton</t>
         </is>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
@@ -4062,24 +4102,28 @@
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>After 08/22 and 08/30 Sum of the Parts reviews, Board finds separate segment sales unlikely to beat a whole-company sale but keeps alternatives open; asks J.P. Morgan to request an updated proposal from Party K.</t>
+          <t>Due date for merger agreement markups; Parent and Party A both delivered on the day. Bidding continued to the 09/15 due date.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>“the Board therefore instructed J.P. Morgan to request an updated proposal from Party K regarding its possible acquisition of Kraton’s chemical segment” (p. 38)</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="n"/>
+          <t>“On September 8, 2021, Parent and Party A submitted their markups of the draft merger agreement.” (p. 38)</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="3" t="n">
-        <v>44438</v>
+        <v>44447</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>44438</v>
+        <v>44447</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>44438</v>
+        <v>44447</v>
       </c>
     </row>
     <row r="55">
@@ -4093,7 +4137,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
+          <t>Parent (DL Chemical Co., Ltd.)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -4110,7 +4154,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="n"/>
@@ -4124,12 +4168,12 @@
       <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Parent submits merger agreement markup, no new price: deletes hell-or-high-water; company termination fee 3.5% of enterprise value (vs 2% equity); no financing condition, but delayed debt marketing period and specific performance/damages as sole recourse on financing failure.</t>
+          <t>Submits merger agreement markup supporting its $45.00 indication (#40): deletes hell-or-high-water, seeks 3.5% of enterprise value company fee (vs 2% of equity), no financing condition but debt marketing period and specific performance/damages as Kraton's only recourse on financing failure.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>“On September 8, 2021, Parent and Party A submitted their markups of the draft merger agreement.” (p. 38)</t>
+          <t>“Parent’s markup deleted the “hell or high water” regulatory provisions included in the Company’s draft merger agreement” (p. 38)</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
@@ -4176,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="n"/>
@@ -4190,7 +4234,7 @@
       <c r="O56" s="2" t="n"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Party A submits its merger agreement markup on the markup due date, no new price; contents not described.</t>
+          <t>Submits its merger agreement markup, supporting its $45.00 indication (#38); terms of the markup not described.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -4242,7 +4286,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n"/>
@@ -4268,7 +4312,7 @@
       <c r="O57" s="2" t="n"/>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Heavy: subject to further diligence and price adjustments; no debt financing talks and no equity financing arrangements. Requested update (#53): chemical segment at 9.5x trailing-12-month (Sept 2021) segment adjusted EBITDA, purported enterprise value $1.25 billion.</t>
+          <t>Heavy: subject to further diligence and price adjustments; no debt financing discussions and no equity financing arranged. Chemical segment at 9.5x adjusted EBITDA for the 12 months to September 2021, which K put at about $1.25 billion enterprise value. Revises #27.</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -4278,7 +4322,7 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S57" s="2" t="n"/>
@@ -4303,42 +4347,64 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Kraton (target)</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n"/>
+          <t>Parent (DL Chemical Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n"/>
-      <c r="J58" s="2" t="n"/>
-      <c r="K58" s="2" t="n"/>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N58" s="2" t="n"/>
       <c r="O58" s="2" t="n"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Due date for final indications of interest (markups were due 09/08/2021). Parent bid on the day; Party A bid on 09/17/2021 and the Board reviewed it 09/18/2021.</t>
+          <t>Light: Parent said it had completed substantially all diligence; financing not a condition in its markup, no commitment yet reported. Formal: final-round bid backed by its 09/08 markup (#54). Revises #40.</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>“and final indications of interest by September 15, 2021” (p. 37)</t>
+          <t>“On September 15, 2021, Parent provided a revised proposal to acquire Kraton for $46.00 per share. Parent noted that it had completed substantially all due diligence.” (p. 39)</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="S58" s="2" t="n"/>
@@ -4363,64 +4429,42 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Kraton</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="n"/>
       <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Light: Parent says it has completed substantially all due diligence; financing not a condition (markup #54). Formal: markup plus response to final-bid letter. $46.00 per share, up from $45.00 (#41).</t>
+          <t>Due date for final indications. Parent bid on the day; Party A bid two days late (#59) and the Board considered it on 09/18.</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>“On September 15, 2021, Parent provided a revised proposal to acquire Kraton for $46.00 per share. Parent noted that it had completed substantially all due diligence.” (p. 39)</t>
+          <t>“final indications of interest by September 15, 2021” (p. 37)</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="S59" s="2" t="n"/>
@@ -4462,7 +4506,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H60" s="4" t="n">
         <v>40.5</v>
@@ -4492,7 +4536,7 @@
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Heavy: 'subject to additional due diligence'. Formal: markup (#55) plus final-round response, two days after the 09/15 due date. $40.50 per share, down from $45.00 (#39).</t>
+          <t>Heavy: subject to additional due diligence. Formal: final-round bid backed by its 09/08 markup (#55), two days after the due date. Revises #38 downward from $45.00.</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -4502,7 +4546,7 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>Q4; Q9</t>
+          <t>Q7; Q8</t>
         </is>
       </c>
       <c r="S60" s="2" t="n"/>
@@ -4544,7 +4588,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="n"/>
@@ -4570,7 +4614,7 @@
       <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Heavy: subject to additional due diligence and adjustments. Alternative to #59: buys the polymer segment at $1.3 billion enterprise value while the chemical business is spun off to Kraton stockholders.</t>
+          <t>Heavy: subject to additional due diligence and adjustments. Alternative to #59: buy the polymer segment for $1.3 billion enterprise value, with the chemical business spun off to Kraton stockholders. No per-share price.</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -4578,7 +4622,11 @@
           <t>“Party A also proposed an alternative transaction whereby it would acquire Kraton’s polymer segment for an enterprise value equal to $1.3 billion, subject to certain adjustments” (p. 39)</t>
         </is>
       </c>
-      <c r="R61" s="2" t="n"/>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q8</t>
+        </is>
+      </c>
       <c r="S61" s="2" t="n"/>
       <c r="T61" s="3" t="n">
         <v>44456</v>
@@ -4601,7 +4649,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
+          <t>Parent (DL Chemical Co., Ltd.)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4618,7 +4666,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="n"/>
@@ -4632,12 +4680,12 @@
       <c r="O62" s="2" t="n"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Price requirement: Board asks Parent to raise to $46.50 and says Kraton expects a reverse break fee on debt financing failure. Board again rejects Sum of the Parts (updated best case about $46–$48 per share).</t>
+          <t>Price requirement: Board tells J.P. Morgan to ask Parent to raise to $46.50 and to say Kraton expects a reverse break fee on a debt financing failure. Board again rejects a sum-of-the-parts sale (best case about $46–$48).</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>“the Board instructed J.P. Morgan to request that Parent increase its proposal to $46.50 per share, and to also inform Party A that its proposal did not provide adequate value” (p. 39)</t>
+          <t>“the Board instructed J.P. Morgan to request that Parent increase its proposal to $46.50 per share” (p. 39)</t>
         </is>
       </c>
       <c r="R62" s="2" t="n"/>
@@ -4680,7 +4728,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
@@ -4694,12 +4742,12 @@
       <c r="O63" s="2" t="n"/>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Board tells Party A its $40.50 proposal (#59) does not offer adequate value; Party A stays in.</t>
+          <t>Board tells J.P. Morgan to inform Party A that its proposals (#59, #60) do not provide adequate value. Party A stays in and bids again.</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>“and to also inform Party A that its proposal did not provide adequate value to Kraton and its stockholders.” (p. 39)</t>
+          <t>“to also inform Party A that its proposal did not provide adequate value to Kraton and its stockholders” (p. 39)</t>
         </is>
       </c>
       <c r="R63" s="2" t="n"/>
@@ -4725,7 +4773,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
+          <t>Parent (DL Chemical Co., Ltd.)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -4742,7 +4790,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H64" s="4" t="n">
         <v>46.5</v>
@@ -4772,7 +4820,7 @@
       <c r="O64" s="2" t="n"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Light: diligence substantially complete (#58); only final documentation remained, negotiated 09/20–09/26 (termination fees settled at $63 million each way). Formal. Raises to the requested $46.50 per share, stated as best and final.</t>
+          <t>Light: diligence substantially complete (#57); debt commitment letter still in draft. Meets the Board's $46.50 request; stated as best and final. Formal. Kraton then sends a revised draft agreement to Parent's counsel; fees negotiated to 09/26.</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -4780,7 +4828,11 @@
           <t>“Parent would increase its purchase price to $46.50 per share, and that this proposal was its best and final offer.” (p. 39)</t>
         </is>
       </c>
-      <c r="R64" s="2" t="n"/>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
       <c r="S64" s="2" t="n"/>
       <c r="T64" s="3" t="n">
         <v>44459</v>
@@ -4803,7 +4855,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>O’Melveny &amp; Myers LLP (Parent)</t>
+          <t>O’Melveny &amp; Myers LLP</t>
         </is>
       </c>
       <c r="D65" s="2" t="n"/>
@@ -4816,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="n"/>
@@ -4828,12 +4880,12 @@
       <c r="O65" s="2" t="n"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Parent's legal counsel; first shown acting 09/20/2021, when it received King &amp; Spalding's revised merger agreement draft.</t>
+          <t>Parent's legal counsel; first shown receiving Kraton's revised draft merger agreement on 09/20/2021.</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>“O’Melveny &amp; Myers LLP, as counsel to Parent” (p. 39)</t>
+          <t>“King &amp; Spalding LLP provided a revised draft of the merger agreement to O’Melveny &amp; Myers LLP, as counsel to Parent” (p. 39)</t>
         </is>
       </c>
       <c r="R65" s="2" t="n"/>
@@ -4876,12 +4928,14 @@
         <v>1</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H66" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="I66" s="2" t="n"/>
+      <c r="I66" s="4" t="n">
+        <v>42</v>
+      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -4904,7 +4958,7 @@
       <c r="O66" s="2" t="n"/>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Unclear: no condition stated, but Party A's diligence was still open (#59, #67). Formal (markup on file). $42.00 per share plus an earnout paid if the chemical segment is sold above thresholds; Price low only.</t>
+          <t>Unclear: no condition stated, though its next bid “remained” subject to diligence. $42.00 plus an earnout paying extra if the chemical segment sells above thresholds. Formal (markup #55). Revises #59.</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -4914,7 +4968,7 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="S66" s="2" t="n"/>
@@ -4956,7 +5010,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="n"/>
@@ -4970,7 +5024,7 @@
       <c r="O67" s="2" t="n"/>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Board, citing risks and contingencies and stockholders not sharing fully in chemical-sale value under the earnout, tells Party A its proposal (#65) does not offer adequate value.</t>
+          <t>Board, citing the earnout's risks and contingencies and that stockholders would not share all chemical-sale value, tells J.P. Morgan to inform Party A its proposal is inadequate.</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -5018,12 +5072,14 @@
         <v>1</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="I68" s="2" t="n"/>
+      <c r="I68" s="4" t="n">
+        <v>44</v>
+      </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -5046,15 +5102,19 @@
       <c r="O68" s="2" t="n"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>Light: only confirmatory due diligence. Formal; stated best and final. $44.00 per share plus revised earnout: 50% of net proceeds above thresholds if Kraton agrees to sell the chemical business before closing. Price low only.</t>
+          <t>Light: subject only to confirmatory diligence. $44.00 plus 50% of net chemical-sale proceeds above thresholds if a sale is agreed before closing. Stated as best and final. Formal (markup #55). Revises #65.</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>“On September 24, 2021, Party A submitted an updated proposal whereby it would acquire Kraton for $44.00 per share.” (p. 40)</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="n"/>
+          <t>“Party A stated that this proposal was its best and final offer and that it remained subject to confirmatory due diligence.” (p. 40)</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
       <c r="S68" s="2" t="n"/>
       <c r="T68" s="3" t="n">
         <v>44463</v>
@@ -5072,42 +5132,48 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>by 09/27/2021</t>
+          <t>09/27/2021</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs (Asia) L.L.C., Seoul Branch (Parent)</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="n"/>
+          <t>Parent (DL Chemical Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="n"/>
       <c r="J69" s="2" t="n"/>
       <c r="K69" s="2" t="n"/>
       <c r="L69" s="2" t="n"/>
-      <c r="M69" s="2" t="n"/>
+      <c r="M69" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N69" s="2" t="n"/>
       <c r="O69" s="2" t="n"/>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>Parent's investment banker/broker, from the merger agreement's fees representation (Annex A), not the background. Goldman Sachs Bank USA separately provided Parent's debt commitment (up to $1.75 billion).</t>
+          <t>Financing support: Parent signs a debt commitment letter for up to $1.75 billion with Goldman Sachs Bank USA, the Debt Commitment Party (pp. 7, 42); the merger has no financing condition. From the financing and reasons sections.</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>“Except for Goldman Sachs (Asia) L.L.C., Seoul Branch, there is no investment banker, broker, finder or other intermediary that has been retained by” (p. A-37)</t>
+          <t>“the financial strength of Parent and Goldman Sachs Bank USA, which provided the Debt Commitment Letter” (p. 42)</t>
         </is>
       </c>
       <c r="R69" s="2" t="n"/>
@@ -5115,7 +5181,9 @@
       <c r="T69" s="3" t="n">
         <v>44466</v>
       </c>
-      <c r="U69" s="2" t="n"/>
+      <c r="U69" s="3" t="n">
+        <v>44466</v>
+      </c>
       <c r="V69" s="3" t="n">
         <v>44466</v>
       </c>
@@ -5131,7 +5199,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Parent (DL Chemical)</t>
+          <t>Parent (DL Chemical Co., Ltd.)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -5148,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="n"/>
@@ -5162,12 +5230,12 @@
       <c r="O70" s="2" t="n"/>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>$46.50 per share in cash. Board approved 09/26 after J.P. Morgan's fairness opinion. $63 million company termination fee (~4% of equity value); $63 million reverse fee on debt financing failure; no financing condition.</t>
+          <t>$46.50 per share in cash. Signed before market open after Board approval on 09/26 with J.P. Morgan's fairness opinion. $63 million company termination fee (~4% of equity) and $63 million reverse fee on debt financing failure; no-shop with fiduciary out.</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>“Kraton, Parent, Merger Subsidiary and Intermediate Merger Subsidiary entered into the Merger Agreement” (p. 41)</t>
+          <t>“September 27, 2021, prior to the opening of regular way trading on the NYSE, Kraton, Parent, Merger Subsidiary and Intermediate Merger Subsidiary entered into the Merger Agreement” (p. 41)</t>
         </is>
       </c>
       <c r="R70" s="2" t="n"/>
@@ -5210,7 +5278,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="n"/>
@@ -5228,7 +5296,7 @@
       <c r="O71" s="2" t="n"/>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>Board on 09/26 judged Party A's $44.00-plus-earnout proposal (#67), given its complexity, timing and regulatory risks, not reasonably likely to deliver more value than Parent's.</t>
+          <t>On 09/26 the Board found A's $44.00-plus-earnout offer (#67) not reasonably likely to deliver more value than Parent's $46.50, citing the earnout, complexity, timing and regulatory risk.</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -5276,7 +5344,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="n"/>
@@ -5298,24 +5366,26 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>Chemical-segment proposal (#56) still outstanding at signing; the Board had rejected a Sum of the Parts strategy built partly on it. No reported withdrawal.</t>
+          <t>Segment bidder last reported when the Board reviewed its 09/09 proposal on 09/18 and again preferred a whole-company sale; no further mention before signing.</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>“again determined that a Sum of the Parts Strategy was not likely to deliver greater value for Kraton’s stockholders as compared to what could be achieved” (p. 39)</t>
+          <t>“the Board reviewed the updated proposals submitted by Parent, Party A and Party K” (p. 39)</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S72" s="2" t="n"/>
       <c r="T72" s="3" t="n">
         <v>44466</v>
       </c>
-      <c r="U72" s="2" t="n"/>
+      <c r="U72" s="3" t="n">
+        <v>44457</v>
+      </c>
       <c r="V72" s="3" t="n">
         <v>44466</v>
       </c>
@@ -5348,7 +5418,7 @@
         <v>1</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="n"/>
@@ -5370,7 +5440,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>Party C's $100 million CST proposal (#29) was described as non-withdrawn on 08/30/2021 and never mentioned again; still open at signing.</t>
+          <t>Segment bidder last reported on 08/30 as holding the only other non-withdrawn chemical-segment proposal ($100 million for part of CST); no further mention before signing.</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -5380,14 +5450,16 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S73" s="2" t="n"/>
       <c r="T73" s="3" t="n">
         <v>44466</v>
       </c>
-      <c r="U73" s="2" t="n"/>
+      <c r="U73" s="3" t="n">
+        <v>44438</v>
+      </c>
       <c r="V73" s="3" t="n">
         <v>44466</v>
       </c>
@@ -5398,132 +5470,60 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>by 09/27/2021</t>
+          <t>09/27/2021</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Post-Reuters financial party</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Kraton and Parent</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Merger announced</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G74" s="2" t="n">
-        <v>2</v>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
       </c>
       <c r="H74" s="2" t="n"/>
       <c r="I74" s="2" t="n"/>
       <c r="J74" s="2" t="n"/>
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
-      <c r="M74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M74" s="2" t="n"/>
+      <c r="N74" s="2" t="n"/>
+      <c r="O74" s="2" t="n"/>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>The filing reports it never submitted a proposal; it was invited to bid (#35) but not included in the 07/20 advancing set. Its exit timing is inferred as by signing, because its NDA date is unknown.</t>
+          <t>Both companies issue press releases announcing the merger agreement on the morning of signing.</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>“management but did not submit any proposal with respect to a transaction.” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R74" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>“Kraton and Parent issued press releases announcing execution of the Merger Agreement.” (p. 41)</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="n"/>
       <c r="S74" s="2" t="n"/>
       <c r="T74" s="3" t="n">
         <v>44466</v>
       </c>
-      <c r="U74" s="2" t="n"/>
+      <c r="U74" s="3" t="n">
+        <v>44466</v>
+      </c>
       <c r="V74" s="3" t="n">
         <v>44466</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>09/27/2021</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Kraton (target)</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Merger announced</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="n"/>
-      <c r="I75" s="2" t="n"/>
-      <c r="J75" s="2" t="n"/>
-      <c r="K75" s="2" t="n"/>
-      <c r="L75" s="2" t="n"/>
-      <c r="M75" s="2" t="n"/>
-      <c r="N75" s="2" t="n"/>
-      <c r="O75" s="2" t="n"/>
-      <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>Kraton and Parent issue press releases before the NYSE open.</t>
-        </is>
-      </c>
-      <c r="Q75" s="2" t="inlineStr">
-        <is>
-          <t>“Kraton and Parent issued press releases announcing execution of the Merger Agreement.” (p. 41)</t>
-        </is>
-      </c>
-      <c r="R75" s="2" t="n"/>
-      <c r="S75" s="2" t="n"/>
-      <c r="T75" s="3" t="n">
-        <v>44466</v>
-      </c>
-      <c r="U75" s="3" t="n">
-        <v>44466</v>
-      </c>
-      <c r="V75" s="3" t="n">
-        <v>44466</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V75"/>
+  <autoFilter ref="A1:V74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5534,19 +5534,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5613,22 +5613,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Board directs outreach to 14 listed buyers and launches the first round (two-phase design)</t>
+          <t>Board directs outreach to 14 listed possible acquirers and commencement of the first round of a two-phase process (#8); outreach end of May–June.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>10 NDA signers: 6 strategic (incl. inbound party; presumed Party A, Parent, Party J, Party K) and 4 financial (presumed Party H, Party I). Segment track: Parties C, D, E, G (strategic, CST only).</t>
+          <t>15 units entered: 11 whole-company confidentiality signers — 6 strategic (Party A, Parent, Party J, Party K [chemical segment only], 2 unnamed; the inbound party is among the six) and 5 financial (Party H, Party I, 2 unnamed, plus 1 unnamed post-Reuters signer after 07/06); and 4 segment-only (CST) strategic parties carried from round 0: Parties C, D, E, G.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>06/29/2021</t>
+          <t>06/29/2021 → 07/19/2021 (updated indications, asked of A, H, Parent and I)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Enforced</t>
+          <t>Extended; Enforced</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4 whole-company: Party A $42–45, Party H $41–43, Parent $41, Party I $40. Other-scope: Party K (chemical segment), Party C and Party G (CST portions).</t>
+          <t>5 whole-company bidders: Party A, Party H, Parent, Party I (by 07/02; A, H, Parent revised by 07/19; I held $40.00) and Party J (by 07/19). Segment proposals: Party K (chemical), Party C and Party G (CST portions).</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>4 whole-company bidders asked to update; 1 NDA signer withdrew; D, E withdrew; J and 3–9 other signers (most likely 3) did not submit</t>
+          <t>3 advanced (Party A, Party H, Parent); Party I and Party J not advanced; 1 strategic signer withdrew; 3 signers and the post-Reuters financial signer never bid; D and E withdrew from CST; C, G, K kept in view.</t>
         </is>
       </c>
     </row>
@@ -5655,26 +5655,26 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>44383</v>
+        <v>44397</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Board requires updated, higher IOIs from the four whole-company bidders before selecting the second round</t>
+          <t>Board invites Party A, Party H and Parent to the second round with additional financial and diligence materials (#46).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>4 admitted: Party A, Parent (strategic); Party H, Party I (financial). Still being received, not admitted: Party J (bid 07/19); post-Reuters financial NDA signer (invited, no proposal); Parties C, G, K (proposals held, no revision asked).</t>
+          <t>3: 2 strategic (Party A, Parent), 1 financial (Party H). Segment proposals still being received, not admitted: Party C and Party G (CST), Party K (chemical).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>07/19/2021</t>
+          <t>none stated</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Enforced</t>
+          <t>No deadline stated</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -5684,12 +5684,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4: Party A $45, Party H $42–45, Parent $45, Party J $38–41. Party I refused to raise $40.</t>
+          <t>0 (no bids requested; management meetings week of 08/09)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>three advanced (A, H, Parent); I and J out</t>
+          <t>Final bid procedures letter to the same three opens round 3; Party G withdrew 08/04.</t>
         </is>
       </c>
     </row>
@@ -5701,92 +5701,46 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>44397</v>
+        <v>44419</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Board admits Party A, Party H and Parent to the 'second round' with more diligence material</t>
+          <t>Final bid procedures letter after the 08/11 Board authorization of the draft merger agreement (#48).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3: Party A, Parent (strategic); Party H (financial). Held segment proposals: Party K, Party C, Party G (G withdrew 08/04).</t>
+          <t>3: 2 strategic (Party A, Parent), 1 financial (Party H). Still being received, not admitted: Party K (chemical; update requested 08/30) and Party C (CST).</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>none stated</t>
+          <t>09/08/2021 (merger agreement markups) → 09/15/2021 (final indications)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>No deadline stated</t>
+          <t>Passed without action; Late bids accepted</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Not final</t>
+          <t>Announced as final</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2 whole-company bidders: Parent ($46.00 on 09/15; $46.50 best and final on 09/20) and Party A ($40.50 on 09/17; $42.00 + earnout on 09/21; $44.00 + earnout best and final on 09/24, late after 09/15). Also Party K chemical-segment update (09/09) and Party A polymer-segment alternative (09/17).</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>all three sent the final bid procedures letter</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>44423</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Final bid procedures letter (sent after 08/11, by 08/20): markups due 09/08, final IOIs due 09/15</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3: Party A, Parent (strategic); Party H (financial). Still being received, not admitted: Party K (updated chemical-segment bid on request, 09/09), Party C (standing CST proposal).</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>09/15/2021 (final IOIs; merger agreement markups separately due 09/08/2021)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Late bids accepted</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Announced as final</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2: Parent $46.00 then $46.50 (best and final); Party A $40.50 (+ polymer-segment alternative), $42.00 + earnout, $44.00 + earnout (best and final). Other-scope: Party K.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>signing with Parent 09/27/2021; H withdrew 08/20; A, K, C not selected</t>
+          <t>Signing with Parent 09/27/2021; Party H withdrew 08/20; Party A, Party K and Party C not selected at signing.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J5"/>
+  <autoFilter ref="A1:J4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5797,14 +5751,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
@@ -5854,27 +5808,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: is this one process with four rounds (R1 outreach 05/24; R2 updated-IOI request 07/06; R3 second-round admission 07/20; R4 final bid letter), with the 2020–21 CST divestiture talks as round 0?</t>
+          <t>Should the parties that bid only for parts of Kraton (C, D, E, G for the CST business; K for the chemical segment; A's polymer-segment alternative) be carried as participants, with entries, exits and Other-scope bid rows?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes. Most plausible alternative: merge R3 and R4 into one 'second round' opened 07/20, with the final letter as a Deadline set (moves round-4 rows #50–#73 to round 3). Less plausible: fold the 07/06 request into round 1 (moves #31–#47).</t>
+          <t>Yes, as segment-only participants. C, D, E and G enter through the 05/20/2021 Board decision to review their CST proposals alongside whole-company bids; K through its round-1 proposal as a confidentiality signer. Their prices stay out of the per-share cells: they are total dollars, enterprise values or EBITDA multiples (mixed bases).</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>E6 counts each selection-and-new-request (07/06, p. 35), each information stage (07/20, p. 36), and the first final-bid request (p. 37) as separate rounds. Gap of about two months or more: CST talks 'late 2020 and early 2021' to end-May 2021 outreach, undated. E5: (a) fails, CST parties still in view (p. 33); (b) not established; (c) met on 05/20. One process.</t>
+          <t>p. 33: Board “would review any proposals submitted by Party C, Party D, Party E, and Party G”; p. 35: on 07/06 C, G, K proposals kept for evaluation; p. 37: 08/30 request for K's update; p. 39: K and A segment proposals reviewed on 09/18.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#2, #9, #10, #11, #31, #45, #50</t>
+          <t>#3, #4, #7, #9, #10, #20, #21, #27, #32, #47, #52, #56, #60, #71, #72</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Round counts and finality: merged R3/R4 gives three rounds with the second 'Announced as final'. Merging R2 into R1 treats the 07/19 IOIs as price bargaining rather than a new solicitation.</t>
+          <t>If excluded, round-1 live units fall by four (C, D, E, G) and C, G, K drop out of rounds 2–3; their contact, admission, bid and exit rows would be removed and the Deal facts auction screen is unchanged.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -5887,27 +5841,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Are the named first-round respondents (Party A, Parent, Party J, Party K; Party H, Party I) members of the 10 NDA signers?</t>
+          <t>Process and round map: one process; round 0 to 05/20/2021; round 1 from 05/24/2021; round 2 from 07/20/2021 (diligence stage); round 3 from the final bid procedures letter after 08/11/2021 to signing. Is this right?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Treat them as members, as the ledger does: exactly 1 strategic and 2 financial signers did not submit. Counts are left as ranges (1–5, 2–4) because membership is not stated.</t>
+          <t>Keep it. Alternative boundary: merge rounds 2 and 3, reading the 07/20 invitation as the single “second round” named in the filing; #48 would become Deadline set and #47–#72 relabelled round 2. Treating the 07/06 request (#31) as a new round is unsupported (same four bidders, not final). Gaps of about two months or more: possibly between the undated “early 2021” CST talks (#3, #4) and outreach from end of May 2021 (#11–#14), length unknown; none after 05/24/2021. E5 tests for a split before 05/20/2021: (a) fails, C, D, E and G were kept in view (#7); (b) not shown, no reported end and contacts undated; (c) holds, the 05/20 sale decision. One process.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The process letter went to each NDA signer and the IOIs came 'as part of the first-round process' (pp. 34–35). The filing never says the named bidders signed NDAs.</t>
+          <t>p. 33: 05/24 Board directed contact of 14 and “to commence the first round”; p. 36: 07/20 invitation to the second round with more diligence; p. 37: “final bid procedures letter” requesting markups and final indications; E6 counts the first request for final offers as a new round.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#13, #14, #25, #26, #27, #28</t>
+          <t>#8, #46, #48</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If some named bidders were not signers, they enter on their bid rows, first-round live units rise by up to six, and more signers did not submit.</t>
+          <t>Merging rounds 2 and 3 gives two Rounds lines instead of three; round 2 would then be Announced as final with due dates 09/08 → 09/15, and G's exit (#47) and all later rows would carry round 2.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -5920,27 +5874,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Should segment-only parties (Parties C, D, E, G on CST; Party K on the chemical segment) count as live bidder units?</t>
+          <t>Who is inside the 10 confidentiality signers, and are the residual non-submitters (#28, #29) exact?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Keep them as participants with their own entries and exits, as recorded, but exclude them from whole-company competition in estimation. They can be identified by Other-scope bid rows and the CST/segment Notes.</t>
+          <t>Treat Party A, Parent, Party J and Party K (strategic) and Party H and Party I (financial) as members and keep the exact residuals: 1 strategic and 2 financial signers never bid. The withdrawing signer (#19) is strategic by 6 − 5. Party B's parent may be a signer or a decliner; it is not counted separately in either.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The Board said it would weigh CST proposals against whole-company bids (p. 33) and kept C, G and K proposals in view (p. 35). None bid for the whole company.</t>
+          <t>p. 34: 14 listed parties plus one inbound party were contacted; 10 signed (6 strategic, 4 financial) and 5 declined, so all 15 contacts are accounted for; every named party active in round 1 was therefore a signer. p. 34: nine signers (5 strategic, 4 financial) met management.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#15, #18, #19, #26, #29, #30, #32, #48, #56, #71, #72</t>
+          <t>#13, #14, #15, #16, #17, #28, #29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Excluding them drops C, D, E, G and K rows from live counts; whole-company live units at R2 opening fall from 7 to 4.</t>
+          <t>If J or K reached Kraton outside the reported contacts, the strategic residual would be 2–3 and live units in round 1 would rise by up to two; Count on #28 would become a range.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -5953,27 +5907,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Deadline outcomes: R1 06/29 Enforced; R2 07/19 Enforced; R3 no due date; R4 09/15 Late bids accepted. Are these right?</t>
+          <t>Round 1 deadline outcomes: 06/29/2021 recorded as Extended, 07/19/2021 as Enforced. Correct?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Yes. For R1, 'Late bids accepted' is possible if any IOI came 06/30–07/02, but the filing does not show it. The 09/08 markup date is treated as a document deadline, not a bid due date.</t>
+          <t>Keep. On 07/06 the Board gave A, H, Parent and I a later due date (07/19) in the same round after evaluating the bids in hand; on 07/20 it selected three bidders on the bids in hand. Alternative for 06/29: Late bids accepted, since Party J, a signer given the 06/29 date, bid only by 07/19 (#37) and the Board considered it.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>R1 bids arrived 'By July 2' and the Board acted 07/06 without waiting for Party J (p. 35). R2 responses came 'By July 19' and the Board selected 07/20 (p. 36). Party A bid 09/17, after the 09/15 due date, and the Board reviewed it 09/18 (p. 39).</t>
+          <t>p. 34: process letter asked for initial indications by 06/29; p. 35: indications “By July 2”, J to bid in mid-July, and 07/06 request for updates by 07/19 (printed “2020”); p. 36: 07/20 selection.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#20, #38, #57, #59</t>
+          <t>#18, #22, #30, #31, #37, #42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>If the 09/08 markup date counts as a bid deadline, R4 gets a second outcome (Enforced; both markups on time) and a Deadline row.</t>
+          <t>Deadline outcome for round 1 would read “Late bids accepted; Enforced”; no row or count changes.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -5986,27 +5940,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Party J missed the 06/29 due date, announced a mid-July bid, and bid $38–$41 on 07/19 without being asked. Is 'Did not submit', then 'Re-entered', right?</t>
+          <t>When did the post-Reuters financial signer enter and leave, and was it live beyond round 1?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Yes. The alternative keeps J live throughout as a late round-1 bidder, with no exit or re-entry; either way J is out at the 07/20 selection.</t>
+          <t>Record it as a round-1 entrant (confidentiality agreement after 07/06, undated) that never submitted, with the exit sorted at the 07/20 advancement decision, which named a complete set without it; window kept 07/06–09/27.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>J was not among the four asked for updated IOIs on 07/06 (p. 35); its 07/19 IOI was received (p. 36).</t>
+          <t>pp. 35–36: after the 07/06 Reuters report one financial party “executed a confidentiality agreement … but did not submit any proposal”; p. 36–37: only A, H and Parent received second-round materials and the final bid letter.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#25, #43, #44, #47</t>
+          <t>#34, #35, #36, #45</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Under the alternative, J is live at the R2 opening and its 07/19 bid is round 1, a late bid.</t>
+          <t>If it signed after 07/20 it was never in round 1; it would then be a separate entrant closed as Not selected at signing on 09/27, adding one live unit to rounds 2–3.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -6019,27 +5973,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Post-Reuters financial NDA signer: what exit label and date?</t>
+          <t>How should Party I's and Party J's departures at the 07/20 selection be labelled?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>'Did not submit' by signing (09/27), round 2, as recorded. If its NDA preceded 07/20, 'Dropped by target' on 07/20 is equally defensible.</t>
+          <t>Both Dropped by target (inferred: the complete advancing set A, H, Parent is named). Party I: Would not improve earlier offer, because it was asked on 07/06 for a higher value and refused. Party J: Not stated; it said it would not go above $41.00 but was never asked to improve.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>It signed an NDA and met management after 07/06 but 'did not submit any proposal' (pp. 35–36). Its dates are not given.</t>
+          <t>p. 35: Board required updated indications from A, H, Parent and I; p. 36: I “not willing to increase” $40.00, J “not willing to increase its purchase price beyond this range”; 07/20 invitation to A, H and Parent only.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#36, #37, #73</t>
+          <t>#41, #43, #44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>A 07/20 drop would remove it from live units in rounds 3–4 (live units at R4 opening 6 → 5).</t>
+          <t>J could instead take Would not improve earlier offer or Lower offer than rivals, which records its valuation cap of $41.00 for the model; I's reason could fall to Not stated.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -6052,27 +6006,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Party I's inferred 07/20 drop: should the exit reason be 'Would not improve earlier offer' or 'Not stated'?</t>
+          <t>Round 3 deadline outcomes: 09/08/2021 (markups) Passed without action; 09/15/2021 (final indications) Late bids accepted. Correct?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>'Would not improve earlier offer'. Party I was asked for greater value and refused to raise $40.00.</t>
+          <t>Keep. Both remaining bidders delivered markups on 09/08 and bidding continued to 09/15; Parent bid on 09/15, Party A only on 09/17, and the Board reviewed A's late bid on 09/18.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>E14 gives this reason to a bidder asked to improve that declines, even where the target then chooses rivals. The refusal is reported (p. 36).</t>
+          <t>p. 37: letter requested markups by 09/08 and final indications by 09/15; p. 38: markups 09/08; p. 39: Parent 09/15, A 09/17, Board review 09/18.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#42, #46</t>
+          <t>#48, #53, #58, #59</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>'Not stated' would lose the valuation signal (I's value is about $40).</t>
+          <t>If the markup date is not treated as a bid due date, 09/08 loses its Deadline row and outcome; reading 09/18 as action on the bids in hand would make 09/15 Enforced.</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -6085,66 +6039,33 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Should the 09/08 merger agreement markups be Bid rows carrying the 07/19 price, rather than Other material events?</t>
+          <t>Formality and conditions of the round-3 offers: markups as Other material event rows; Parent 09/15 and 09/20 Formal/Light; A 09/17 Formal/Heavy, 09/21 Formal/Unclear, 09/24 Formal/Light; A's polymer alternative Informal/Heavy.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>No. Record them as events and make the next priced offers (09/15 Parent, 09/17 Party A) the first Formal bids.</t>
+          <t>Keep. The 09/08 markups carried no new price, so they support later bids rather than forming Bid rows. Parent had substantially completed diligence and financing was not a condition; A's 09/24 bid named only confirmatory diligence.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Neither markup came with a price (p. 38). E11 needs a markup with a priced proposal or in support of one; the prices followed a week later.</t>
+          <t>p. 38: Parent's markup (no financing condition, but it required debt financing); Parent “completed substantially all due diligence”; p. 39: A's 09/17 bid “subject to additional due diligence”; p. 40: A 09/24 “subject to confirmatory due diligence”; Board cited regulatory risks.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>#54, #55, #58</t>
+          <t>#54, #55, #57, #59, #60, #63, #65, #67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>As Bid rows, Parent's and Party A's $45.00 would become Formal from 09/08, a week earlier.</t>
+          <t>Parent's bids become Heavy if the unsigned debt commitment (letter still in draft on 09/20) counts as reported absence of commitment; A's 09/24 becomes Heavy if the Board's regulatory-risk concern is an identified obstacle; A's 09/17 becomes Light if “additional” means confirmatory.</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Conditions on Party A's 09/17 and 09/21 bids: Heavy and Unclear?</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Yes. 09/17 'subject to additional due diligence' is Heavy (open-ended, unlike the later 'confirmatory'). 09/21 states no condition while diligence remained open: Unclear.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>On 09/24 Party A described its diligence as confirmatory (p. 40). The 09/17 wording is broader (p. 39). The Board cited 'risks and contingencies' on 09/23 (p. 40).</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>#59, #65</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Light on 09/17 would make Party A's first final-round bid a low-conditionality bid at $40.50.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6182,7 +6103,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Kraton Corporation (NYSE: KRA), Houston, Texas; specialty polymers and pine-based chemicals</t>
+          <t>Kraton Corporation (NYSE: KRA), Houston, Texas; polymer and chemical segments</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6115,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>DL Chemical Co., Ltd. (Parent), a DL Holdings Co., Ltd. subsidiary, through DLC US Holdings, Inc. and DLC US, Inc.</t>
+          <t>DL Chemical Co., Ltd. (“Parent”), Seoul, South Korea, a subsidiary of DL Holdings Co., Ltd., through DLC US Holdings, Inc. and DLC US, Inc.</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6127,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic (South Korean petrochemical operating company)</t>
+          <t>Strategic</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6139,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$46.50 per share in cash; funded with up to $1.75 billion committed debt from Goldman Sachs Bank USA and Parent cash; no financing condition; $63 million termination and reverse termination fees</t>
+          <t>$46.50 per share in cash, without interest; about $2.5 billion of total funds (including refinancing of Kraton debt), from up to $1.75 billion of committed debt financing (Goldman Sachs Bank USA) and Parent's cash; no financing condition</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6163,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/27/2021 (press releases before the NYSE open)</t>
+          <t>09/27/2021</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6175,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DEFM14A definitive proxy statement, dated 11/04/2021</t>
+          <t>DEFM14A (definitive proxy statement), 11/04/2021</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6223,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>None reported. Before the 05/20/2021 sale decision, Kraton's 12/2020 corporate development plan sought polymer acquisitions (Parties A and B declined; no rows) and a CST divestiture (Parties C–G; recorded as round 0).</t>
+          <t>None reported for the whole company. From December 2020 Kraton pursued a corporate development plan: buying or combining with the polymer businesses of Parties A and B (both declined) and selling its CST business (Parties C, D, E, F, G approached); the CST track carried into process 1 as round 0 (#2–#4, #7). Parent had bought Kraton's Cariflex business in March 2020.</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6235,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 11 parties (10 by late June 2021, 6 strategic and 4 financial, plus 1 post-Reuters financial party)</t>
+          <t>Met (process 1): 11 parties (10 by late June 2021 — 6 strategic, 4 financial — plus 1 financial party after 07/06/2021)</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6247,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Yes. Also other-scope bids: Party K (chemical segment), Parties C and G (portions of the CST business), Party A's alternative (polymer segment with chemical spin-off)</t>
+          <t>Yes (also segment bids: Parties C and G for portions of the CST business, Party K for the chemical segment, Party A's alternative for the polymer segment)</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6259,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars per share for whole-company bids. Segment bids are stated as totals, EBITDA multiples or enterprise values (see Notes). Party A bids of 09/21 and 09/24 add an unquantified earnout.</t>
+          <t>US dollars per share for whole-company bids; segment bids in total US dollars, enterprise value or multiples of segment EBITDA (mixed bases; see Q1). Party A's last two bids add an earnout to the per-share price.</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6295,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>After a 2020 strategy review, Kraton sought polymer acquisitions and a sale of its CST business; the effort stalled, and on 05/20/2021 the Board decided to explore a sale of the whole company. J.P. Morgan contacted 14 listed buyers plus one inbound party, and 10 signed NDAs. Four whole-company IOIs ($40–$45) arrived by early July, alongside segment bids from Parties K, C and G. After a round of updated IOIs, Party A, Party H and Parent were taken to a final round; Party H withdrew on 08/20, unable to hold its range. Parent bid $46.00 on 09/15 and, when asked, raised to $46.50 best and final; Party A's lower bids ($40.50, then $42.00 and $44.00 with earnouts) were rejected. Kraton and Parent signed on 09/27/2021 at $46.50 in cash.</t>
+          <t>After a corporate development plan to buy polymer businesses and sell the CST business stalled, Kraton's board decided on 05/20/2021 to explore a sale of the whole company. J.P. Morgan contacted 14 listed parties and received one inbound inquiry; 10 signed confidentiality agreements, and one more financial party signed after a 07/06 Reuters leak. Four indications arrived by early July (Party A $42–45, H $41–43, Parent $41, I $40), and after a request for higher values the board advanced A, H and Parent on 07/20, dropping I and late bidder J. H withdrew on 08/20; in the final round Parent bid $46.00 and then, at the board's request, $46.50 best and final, while Party A bid $40.50 and then $42.00 and $44.00 with chemical-segment earnouts. Segment offers from Parties C, G and K were weighed as a sum-of-the-parts alternative and rejected, and Kraton signed with Parent on 09/27/2021 at $46.50 in cash.</t>
         </is>
       </c>
     </row>
